--- a/Financial Analysis/TM.xlsx
+++ b/Financial Analysis/TM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53634140-4A1B-4748-941B-4F75A210E96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CFA3BB-22F3-43D5-8FA1-8F3C9DDEBEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{293EE719-AEB1-43A9-8AC3-A334237D7F43}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="93">
   <si>
     <t>Price</t>
   </si>
@@ -389,7 +389,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -421,6 +421,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -942,17 +943,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="2">
-        <v>193.01</v>
+        <v>199.06</v>
       </c>
       <c r="E3" s="4">
-        <v>45904</v>
+        <v>45995</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45904</v>
+        <v>45995</v>
       </c>
       <c r="G3" s="4">
-        <v>45959</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
@@ -960,11 +961,11 @@
         <v>1</v>
       </c>
       <c r="D4" s="5">
-        <f>13032.9/10</f>
-        <v>1303.29</v>
+        <f>(15795-2762)/10</f>
+        <v>1303.3</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
@@ -973,7 +974,7 @@
       </c>
       <c r="D5" s="7">
         <f>D3*D4</f>
-        <v>251548.00289999999</v>
+        <v>259434.89799999999</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
@@ -981,11 +982,11 @@
         <v>25</v>
       </c>
       <c r="D6" s="6">
-        <f>8210856+5643887</f>
-        <v>13854743</v>
+        <f>8982404+5798051</f>
+        <v>14780455</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
@@ -993,11 +994,11 @@
         <v>26</v>
       </c>
       <c r="D7" s="6">
-        <f>15505149+22938634</f>
-        <v>38443783</v>
+        <f>15829516+22963363</f>
+        <v>38792879</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
@@ -1006,10 +1007,10 @@
       </c>
       <c r="D8" s="7">
         <f>D6/D13</f>
-        <v>93417.456678578645</v>
+        <v>95499.483103960709</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
@@ -1018,10 +1019,10 @@
       </c>
       <c r="D9" s="7">
         <f>D7/D13</f>
-        <v>259212.34576225473</v>
+        <v>250648.56884409121</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
@@ -1030,10 +1031,10 @@
       </c>
       <c r="D10" s="7">
         <f>(D6-D7)/D13</f>
-        <v>-165794.88908367607</v>
+        <v>-155149.08574013051</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
@@ -1042,7 +1043,7 @@
       </c>
       <c r="D11" s="7">
         <f>D5-D10</f>
-        <v>417342.89198367606</v>
+        <v>414583.9837401305</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.3">
@@ -1050,13 +1051,13 @@
         <v>8</v>
       </c>
       <c r="D13" s="9">
-        <v>148.31</v>
+        <v>154.77000000000001</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="I15" s="9">
         <f>(2766-43+47)*(6886/D13)+(43/2)*D3</f>
-        <v>132760.19305272741</v>
+        <v>127522.14963041931</v>
       </c>
     </row>
   </sheetData>
@@ -1068,7 +1069,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F5E7229-131C-44E2-A523-FFFDA163C314}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="B1:EI48"/>
+  <dimension ref="B1:EI67"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.109375" bestFit="1" customWidth="1"/>
@@ -1372,35 +1373,35 @@
       </c>
       <c r="C3" s="10">
         <f>C32/Main!$D$13</f>
-        <v>52061.715326006335</v>
+        <v>49888.69289914066</v>
       </c>
       <c r="D3" s="10">
         <f>D32/Main!$D$13</f>
-        <v>51493.520329040519</v>
+        <v>49344.213994960257</v>
       </c>
       <c r="E3" s="10">
         <f>E32/Main!$D$13</f>
-        <v>51304.234373946463</v>
+        <v>49162.828713574978</v>
       </c>
       <c r="F3" s="10">
         <f>F32/Main!$D$13</f>
-        <v>46519.715460859014</v>
+        <v>44578.01253472895</v>
       </c>
       <c r="G3" s="10">
         <f>G32/Main!$D$13</f>
-        <v>31021.482030881263</v>
+        <v>29726.665374426568</v>
       </c>
       <c r="H3" s="10">
         <f>H32/Main!$D$13</f>
-        <v>45677.479603533138</v>
+        <v>43770.931058990755</v>
       </c>
       <c r="I3" s="10">
         <f>I32/Main!$D$13</f>
-        <v>54952.680196884903</v>
+        <v>52658.990760483292</v>
       </c>
       <c r="J3" s="10">
         <f>F3*1.15</f>
-        <v>53497.672779987864</v>
+        <v>51264.714414938288</v>
       </c>
       <c r="K3" s="10"/>
       <c r="L3" s="10"/>
@@ -1416,93 +1417,99 @@
       <c r="V3" s="10"/>
       <c r="W3" s="10">
         <f>W32/Main!$D$13</f>
-        <v>79818.481558896907</v>
-      </c>
-      <c r="X3" s="10"/>
+        <v>76486.909607805123</v>
+      </c>
+      <c r="X3" s="10">
+        <f>X32/Main!$D$13</f>
+        <v>73945.667765070742</v>
+      </c>
       <c r="Y3" s="10"/>
       <c r="Z3" s="10"/>
       <c r="AA3" s="10">
         <f>AA32/Main!$D$13</f>
-        <v>82619.688490324319</v>
-      </c>
-      <c r="AB3" s="10"/>
+        <v>79171.195968210886</v>
+      </c>
+      <c r="AB3" s="10">
+        <f>AB32/Main!$D$13</f>
+        <v>79973.037410350837</v>
+      </c>
       <c r="AC3" s="10"/>
       <c r="AD3" s="10"/>
       <c r="AF3" s="10">
         <f>AF32/Main!$D$13</f>
-        <v>186077.76279414739</v>
+        <v>178310.99696323575</v>
       </c>
       <c r="AG3" s="10">
         <f>AG32/Main!$D$13</f>
-        <v>198095.27341379542</v>
+        <v>189826.90443884474</v>
       </c>
       <c r="AH3" s="10">
         <f>AH32/Main!$D$13</f>
-        <v>203800.69449126828</v>
+        <v>195294.18491955803</v>
       </c>
       <c r="AI3" s="10">
         <f>AI32/Main!$D$13</f>
-        <v>201379.18548985233</v>
+        <v>192973.74814240486</v>
       </c>
       <c r="AJ3" s="10">
         <f>AJ32/Main!$D$13</f>
-        <v>183498.03789360123</v>
+        <v>175838.94811656006</v>
       </c>
       <c r="AK3" s="10">
         <f>AK32/Main!$D$13</f>
-        <v>211580.52053131952</v>
+        <v>202749.28603734574</v>
       </c>
       <c r="AL3" s="10">
         <f>AL32/Main!$D$13</f>
-        <v>250517.82078079699</v>
+        <v>240061.36848226399</v>
       </c>
       <c r="AM3" s="10">
         <f>AM32/Main!$D$13</f>
-        <v>304061.25682691659</v>
+        <v>291369.93603411515</v>
       </c>
       <c r="AN3" s="10">
         <f>AN32/Main!$D$13</f>
-        <v>323893.89791652618</v>
+        <v>310374.77547328291</v>
       </c>
       <c r="AO3" s="10">
         <f>AN3*1.04</f>
-        <v>336849.65383318724</v>
+        <v>322789.76649221423</v>
       </c>
       <c r="AP3" s="10">
         <f>AO3*1.02</f>
-        <v>343586.646909851</v>
+        <v>329245.56182205852</v>
       </c>
       <c r="AQ3" s="10">
         <f>AP3*1.01</f>
-        <v>347022.51337894949</v>
+        <v>332538.01744027913</v>
       </c>
       <c r="AR3" s="10">
         <f t="shared" ref="AR3:AS3" si="0">AQ3*1.01</f>
-        <v>350492.73851273896</v>
+        <v>335863.39761468192</v>
       </c>
       <c r="AS3" s="10">
         <f t="shared" si="0"/>
-        <v>353997.66589786636</v>
+        <v>339222.03159082873</v>
       </c>
       <c r="AT3" s="10">
         <f t="shared" ref="AT3" si="1">AS3*1.01</f>
-        <v>357537.64255684504</v>
+        <v>342614.25190673704</v>
       </c>
       <c r="AU3" s="10">
         <f t="shared" ref="AU3" si="2">AT3*1.01</f>
-        <v>361113.01898241352</v>
+        <v>346040.39442580444</v>
       </c>
       <c r="AV3" s="10">
         <f t="shared" ref="AV3" si="3">AU3*1.01</f>
-        <v>364724.14917223767</v>
+        <v>349500.79837006249</v>
       </c>
       <c r="AW3" s="10">
         <f t="shared" ref="AW3" si="4">AV3*1.01</f>
-        <v>368371.39066396008</v>
+        <v>352995.8063537631</v>
       </c>
       <c r="AX3" s="10">
         <f t="shared" ref="AX3" si="5">AW3*1.01</f>
-        <v>372055.10457059968</v>
+        <v>356525.76441730076</v>
       </c>
     </row>
     <row r="4" spans="2:50" x14ac:dyDescent="0.3">
@@ -1511,35 +1518,35 @@
       </c>
       <c r="C4" s="5">
         <f>C33/Main!$D$13</f>
-        <v>42270.548176117591</v>
+        <v>40506.202752471407</v>
       </c>
       <c r="D4" s="5">
         <f>D33/Main!$D$13</f>
-        <v>42380.230598071605</v>
+        <v>40611.30710085934</v>
       </c>
       <c r="E4" s="5">
         <f>E33/Main!$D$13</f>
-        <v>41984.734677364977</v>
+        <v>40232.318924856234</v>
       </c>
       <c r="F4" s="5">
         <f>F33/Main!$D$13</f>
-        <v>38460.238689232014</v>
+        <v>36854.933126574913</v>
       </c>
       <c r="G4" s="5">
         <f>G33/Main!$D$13</f>
-        <v>27316.890297350146</v>
+        <v>26176.700911029267</v>
       </c>
       <c r="H4" s="5">
         <f>H33/Main!$D$13</f>
-        <v>37935.944980109227</v>
+        <v>36352.523098791753</v>
       </c>
       <c r="I4" s="5">
         <f>I33/Main!$D$13</f>
-        <v>43782.145506034656</v>
+        <v>41954.706984557728</v>
       </c>
       <c r="J4" s="5">
         <f>J3-J5</f>
-        <v>43868.091679590048</v>
+        <v>42037.065820249394</v>
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
@@ -1555,93 +1562,99 @@
       <c r="V4" s="5"/>
       <c r="W4" s="5">
         <f>W33/Main!$D$13</f>
-        <v>63441.332344413728</v>
-      </c>
-      <c r="X4" s="5"/>
+        <v>60793.332041093228</v>
+      </c>
+      <c r="X4" s="5">
+        <f>X33/Main!$D$13</f>
+        <v>58192.996058667697</v>
+      </c>
       <c r="Y4" s="5"/>
       <c r="Z4" s="5"/>
       <c r="AA4" s="5">
         <f>AA33/Main!$D$13</f>
-        <v>67814.125817544336</v>
-      </c>
-      <c r="AB4" s="5"/>
+        <v>64983.607934354201</v>
+      </c>
+      <c r="AB4" s="5">
+        <f>AB33/Main!$D$13</f>
+        <v>67251.98035795051</v>
+      </c>
       <c r="AC4" s="5"/>
       <c r="AD4" s="5"/>
       <c r="AF4" s="5">
         <f>AF33/Main!$D$13</f>
-        <v>153289.29944036141</v>
+        <v>146891.10292692381</v>
       </c>
       <c r="AG4" s="5">
         <f>AG33/Main!$D$13</f>
-        <v>161075.80743038229</v>
+        <v>154352.60709439812</v>
       </c>
       <c r="AH4" s="5">
         <f>AH33/Main!$D$13</f>
-        <v>167094.49801092307</v>
+        <v>160120.08141112619</v>
       </c>
       <c r="AI4" s="5">
         <f>AI33/Main!$D$13</f>
-        <v>165095.75214078618</v>
+        <v>158204.76190476189</v>
       </c>
       <c r="AJ4" s="5">
         <f>AJ33/Main!$D$13</f>
-        <v>150915.11024206056</v>
+        <v>144616.01085481682</v>
       </c>
       <c r="AK4" s="5">
         <f>AK33/Main!$D$13</f>
-        <v>171315.71707909109</v>
+        <v>164165.10951734832</v>
       </c>
       <c r="AL4" s="5">
         <f>AL33/Main!$D$13</f>
-        <v>207951.46652282382</v>
+        <v>199271.70640304967</v>
       </c>
       <c r="AM4" s="5">
         <f>AM33/Main!$D$13</f>
-        <v>240894.12042343739</v>
+        <v>230839.35517219099</v>
       </c>
       <c r="AN4" s="5">
         <f>AN33/Main!$D$13</f>
-        <v>259312.69637920571</v>
+        <v>248489.1516443755</v>
       </c>
       <c r="AO4" s="5">
         <f t="shared" ref="AO4:AS4" si="6">AO3-AO5</f>
-        <v>272848.21960488165</v>
+        <v>267915.50618853781</v>
       </c>
       <c r="AP4" s="5">
         <f t="shared" si="6"/>
-        <v>278305.18399697932</v>
+        <v>273273.81631230854</v>
       </c>
       <c r="AQ4" s="5">
         <f t="shared" si="6"/>
-        <v>281088.23583694908</v>
+        <v>272681.17430102889</v>
       </c>
       <c r="AR4" s="5">
         <f t="shared" si="6"/>
-        <v>283899.11819531856</v>
+        <v>272049.35206789232</v>
       </c>
       <c r="AS4" s="5">
         <f t="shared" si="6"/>
-        <v>286738.10937727173</v>
+        <v>274769.84558857128</v>
       </c>
       <c r="AT4" s="5">
         <f t="shared" ref="AT4:AX4" si="7">AT3-AT5</f>
-        <v>289605.4904710445</v>
+        <v>277517.54404445703</v>
       </c>
       <c r="AU4" s="5">
         <f t="shared" si="7"/>
-        <v>292501.54537575494</v>
+        <v>280292.71948490158</v>
       </c>
       <c r="AV4" s="5">
         <f t="shared" si="7"/>
-        <v>295426.56082951254</v>
+        <v>283095.64667975064</v>
       </c>
       <c r="AW4" s="5">
         <f t="shared" si="7"/>
-        <v>298380.82643780764</v>
+        <v>285926.60314654809</v>
       </c>
       <c r="AX4" s="5">
         <f t="shared" si="7"/>
-        <v>301364.63470218575</v>
+        <v>288785.86917801364</v>
       </c>
     </row>
     <row r="5" spans="2:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1650,35 +1663,35 @@
       </c>
       <c r="C5" s="10">
         <f>C34/Main!$D$13</f>
-        <v>9791.1671498887463</v>
+        <v>9382.49014666925</v>
       </c>
       <c r="D5" s="10">
         <f>D34/Main!$D$13</f>
-        <v>9113.289730968916</v>
+        <v>8732.9068941009227</v>
       </c>
       <c r="E5" s="10">
         <f>E34/Main!$D$13</f>
-        <v>9319.4996965814844</v>
+        <v>8930.5097887187439</v>
       </c>
       <c r="F5" s="10">
         <f>F34/Main!$D$13</f>
-        <v>8059.4767716269971</v>
+        <v>7723.0794081540344</v>
       </c>
       <c r="G5" s="10">
         <f>G34/Main!$D$13</f>
-        <v>3704.5917335311174</v>
+        <v>3549.9644633972989</v>
       </c>
       <c r="H5" s="10">
         <f>H34/Main!$D$13</f>
-        <v>7741.5346234239096</v>
+        <v>7418.4079601990043</v>
       </c>
       <c r="I5" s="10">
         <f>I34/Main!$D$13</f>
-        <v>11170.534690850245</v>
+        <v>10704.283775925567</v>
       </c>
       <c r="J5" s="10">
         <f>J3*0.18</f>
-        <v>9629.581100397816</v>
+        <v>9227.6485946888915</v>
       </c>
       <c r="K5" s="10"/>
       <c r="L5" s="10"/>
@@ -1694,93 +1707,99 @@
       <c r="V5" s="10"/>
       <c r="W5" s="10">
         <f>W34/Main!$D$13</f>
-        <v>16377.149214483177</v>
-      </c>
-      <c r="X5" s="10"/>
+        <v>15693.577566711894</v>
+      </c>
+      <c r="X5" s="10">
+        <f>X34/Main!$D$13</f>
+        <v>15752.671706403049</v>
+      </c>
       <c r="Y5" s="10"/>
       <c r="Z5" s="10"/>
       <c r="AA5" s="10">
         <f>AA34/Main!$D$13</f>
-        <v>14805.562672779988</v>
-      </c>
-      <c r="AB5" s="10"/>
+        <v>14187.588033856689</v>
+      </c>
+      <c r="AB5" s="10">
+        <f>AB34/Main!$D$13</f>
+        <v>12721.057052400336</v>
+      </c>
       <c r="AC5" s="10"/>
       <c r="AD5" s="10"/>
       <c r="AF5" s="10">
         <f>AF34/Main!$D$13</f>
-        <v>32788.463353785992</v>
+        <v>31419.894036311944</v>
       </c>
       <c r="AG5" s="10">
         <f>AG34/Main!$D$13</f>
-        <v>37019.465983413123</v>
+        <v>35474.297344446597</v>
       </c>
       <c r="AH5" s="10">
         <f>AH34/Main!$D$13</f>
-        <v>36706.196480345221</v>
+        <v>35174.103508431865</v>
       </c>
       <c r="AI5" s="10">
         <f>AI34/Main!$D$13</f>
-        <v>36283.433349066145</v>
+        <v>34768.986237642952</v>
       </c>
       <c r="AJ5" s="10">
         <f>AJ34/Main!$D$13</f>
-        <v>32582.927651540693</v>
+        <v>31222.937261743231</v>
       </c>
       <c r="AK5" s="10">
         <f>AK34/Main!$D$13</f>
-        <v>40264.803452228443</v>
+        <v>38584.176519997411</v>
       </c>
       <c r="AL5" s="10">
         <f>AL34/Main!$D$13</f>
-        <v>42566.354257973166</v>
+        <v>40789.662079214315</v>
       </c>
       <c r="AM5" s="10">
         <f>AM34/Main!$D$13</f>
-        <v>63167.136403479199</v>
+        <v>60530.580861924143</v>
       </c>
       <c r="AN5" s="10">
         <f>AN34/Main!$D$13</f>
-        <v>64581.201537320478</v>
+        <v>61885.62382890741</v>
       </c>
       <c r="AO5" s="10">
-        <f>AO3*0.19</f>
-        <v>64001.434228305574</v>
+        <f>AO3*0.17</f>
+        <v>54874.260303676419</v>
       </c>
       <c r="AP5" s="10">
-        <f t="shared" ref="AP5:AX5" si="8">AP3*0.19</f>
-        <v>65281.462912871692</v>
+        <f>AP3*0.17</f>
+        <v>55971.745509749955</v>
       </c>
       <c r="AQ5" s="10">
-        <f t="shared" si="8"/>
-        <v>65934.277542000404</v>
+        <f>AQ3*0.18</f>
+        <v>59856.843139250239</v>
       </c>
       <c r="AR5" s="10">
-        <f t="shared" si="8"/>
-        <v>66593.620317420398</v>
+        <f>AR3*0.19</f>
+        <v>63814.045546789566</v>
       </c>
       <c r="AS5" s="10">
-        <f t="shared" si="8"/>
-        <v>67259.556520594604</v>
+        <f t="shared" ref="AP5:AX5" si="8">AS3*0.19</f>
+        <v>64452.186002257462</v>
       </c>
       <c r="AT5" s="10">
         <f t="shared" si="8"/>
-        <v>67932.152085800553</v>
+        <v>65096.70786228004</v>
       </c>
       <c r="AU5" s="10">
         <f t="shared" si="8"/>
-        <v>68611.473606658576</v>
+        <v>65747.674940902842</v>
       </c>
       <c r="AV5" s="10">
         <f t="shared" si="8"/>
-        <v>69297.588342725154</v>
+        <v>66405.151690311875</v>
       </c>
       <c r="AW5" s="10">
         <f t="shared" si="8"/>
-        <v>69990.564226152419</v>
+        <v>67069.203207214989</v>
       </c>
       <c r="AX5" s="10">
         <f t="shared" si="8"/>
-        <v>70690.469868413944</v>
+        <v>67739.895239287143</v>
       </c>
     </row>
     <row r="6" spans="2:50" x14ac:dyDescent="0.3">
@@ -1789,35 +1808,35 @@
       </c>
       <c r="C6" s="5">
         <f>C35/Main!$D$13</f>
-        <v>4797.4984829074237</v>
+        <v>4597.253989791303</v>
       </c>
       <c r="D6" s="5">
         <f>D35/Main!$D$13</f>
-        <v>4672.543995684714</v>
+        <v>4477.5150222911416</v>
       </c>
       <c r="E6" s="5">
         <f>E35/Main!$D$13</f>
-        <v>5003.560110579192</v>
+        <v>4794.7147379983198</v>
       </c>
       <c r="F6" s="5">
         <f>F35/Main!$D$13</f>
-        <v>5632.6950306789831</v>
+        <v>5397.5899722168379</v>
       </c>
       <c r="G6" s="5">
         <f>G35/Main!$D$13</f>
-        <v>3610.7342728069584</v>
+        <v>3460.0245525618657</v>
       </c>
       <c r="H6" s="5">
         <f>H35/Main!$D$13</f>
-        <v>4329.3506843773175</v>
+        <v>4148.6463784971247</v>
       </c>
       <c r="I6" s="5">
         <f>I35/Main!$D$13</f>
-        <v>4509.2171802305984</v>
+        <v>4321.0053627964071</v>
       </c>
       <c r="J6" s="5">
         <f>F6*0.92</f>
-        <v>5182.0794282246643</v>
+        <v>4965.7827744394908</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
@@ -1833,93 +1852,99 @@
       <c r="V6" s="5"/>
       <c r="W6" s="5">
         <f>W35/Main!$D$13</f>
-        <v>7551.6418312993055</v>
-      </c>
-      <c r="X6" s="5"/>
+        <v>7236.4411707695281</v>
+      </c>
+      <c r="X6" s="5">
+        <f>X35/Main!$D$13</f>
+        <v>8288.008011888609</v>
+      </c>
       <c r="Y6" s="5"/>
       <c r="Z6" s="5"/>
       <c r="AA6" s="5">
         <f>AA35/Main!$D$13</f>
-        <v>6942.7010990492881</v>
-      </c>
-      <c r="AB6" s="5"/>
+        <v>6652.9172320217094</v>
+      </c>
+      <c r="AB6" s="5">
+        <f>AB35/Main!$D$13</f>
+        <v>7296.5497189377784</v>
+      </c>
       <c r="AC6" s="5"/>
       <c r="AD6" s="5"/>
       <c r="AF6" s="5">
         <f>AF35/Main!$D$13</f>
-        <v>19341.143550670891</v>
+        <v>18533.856690573106</v>
       </c>
       <c r="AG6" s="5">
         <f>AG35/Main!$D$13</f>
-        <v>20838.075652349806</v>
+        <v>19968.307811591392</v>
       </c>
       <c r="AH6" s="5">
         <f>AH35/Main!$D$13</f>
-        <v>20068.444474411706</v>
+        <v>19230.800542740839</v>
       </c>
       <c r="AI6" s="5">
         <f>AI35/Main!$D$13</f>
-        <v>20106.297619850313</v>
+        <v>19267.073722297602</v>
       </c>
       <c r="AJ6" s="5">
         <f>AJ35/Main!$D$13</f>
-        <v>17764.311239970331</v>
+        <v>17022.840343735865</v>
       </c>
       <c r="AK6" s="5">
         <f>AK35/Main!$D$13</f>
-        <v>20065.922729418111</v>
+        <v>19228.384053757185</v>
       </c>
       <c r="AL6" s="5">
         <f>AL35/Main!$D$13</f>
-        <v>24192.502191355943</v>
+        <v>23182.722749886929</v>
       </c>
       <c r="AM6" s="5">
         <f>AM35/Main!$D$13</f>
-        <v>27074.256624637583</v>
+        <v>25944.194611358787</v>
       </c>
       <c r="AN6" s="5">
         <f>AN35/Main!$D$13</f>
-        <v>32246.321893331537</v>
+        <v>30900.381210828971</v>
       </c>
       <c r="AO6" s="5">
         <f t="shared" ref="AO6" si="9">AN6*1.02</f>
-        <v>32891.24833119817</v>
+        <v>31518.388835045553</v>
       </c>
       <c r="AP6" s="5">
         <f>AO6*1.01</f>
-        <v>33220.160814510149</v>
+        <v>31833.57272339601</v>
       </c>
       <c r="AQ6" s="5">
         <f t="shared" ref="AQ6:AS6" si="10">AP6*1.01</f>
-        <v>33552.362422655249</v>
+        <v>32151.90845062997</v>
       </c>
       <c r="AR6" s="5">
         <f t="shared" si="10"/>
-        <v>33887.886046881802</v>
+        <v>32473.42753513627</v>
       </c>
       <c r="AS6" s="5">
         <f t="shared" si="10"/>
-        <v>34226.764907350618</v>
+        <v>32798.161810487632</v>
       </c>
       <c r="AT6" s="5">
         <f t="shared" ref="AT6" si="11">AS6*1.01</f>
-        <v>34569.032556424121</v>
+        <v>33126.143428592506</v>
       </c>
       <c r="AU6" s="5">
         <f t="shared" ref="AU6" si="12">AT6*1.01</f>
-        <v>34914.72288198836</v>
+        <v>33457.404862878429</v>
       </c>
       <c r="AV6" s="5">
         <f t="shared" ref="AV6" si="13">AU6*1.01</f>
-        <v>35263.870110808246</v>
+        <v>33791.978911507213</v>
       </c>
       <c r="AW6" s="5">
         <f t="shared" ref="AW6" si="14">AV6*1.01</f>
-        <v>35616.508811916327</v>
+        <v>34129.898700622281</v>
       </c>
       <c r="AX6" s="5">
         <f t="shared" ref="AX6" si="15">AW6*1.01</f>
-        <v>35972.673900035494</v>
+        <v>34471.197687628504</v>
       </c>
     </row>
     <row r="7" spans="2:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1928,35 +1953,35 @@
       </c>
       <c r="C7" s="10">
         <f>C36/Main!$D$13</f>
-        <v>4993.6686669813225</v>
+        <v>4785.2361568779479</v>
       </c>
       <c r="D7" s="10">
         <f>D36/Main!$D$13</f>
-        <v>4440.7457352842021</v>
+        <v>4255.3918718097821</v>
       </c>
       <c r="E7" s="10">
         <f>E36/Main!$D$13</f>
-        <v>4315.9395860022923</v>
+        <v>4135.7950507204232</v>
       </c>
       <c r="F7" s="10">
         <f>F36/Main!$D$13</f>
-        <v>2426.7817409480144</v>
+        <v>2325.489435937197</v>
       </c>
       <c r="G7" s="10">
         <f>G36/Main!$D$13</f>
-        <v>93.857460724158855</v>
+        <v>89.939910835433224</v>
       </c>
       <c r="H7" s="10">
         <f>H36/Main!$D$13</f>
-        <v>3412.1839390465916</v>
+        <v>3269.76158170188</v>
       </c>
       <c r="I7" s="10">
         <f>I36/Main!$D$13</f>
-        <v>6661.3175106196477</v>
+        <v>6383.2784131291592</v>
       </c>
       <c r="J7" s="10">
         <f>J5-J6</f>
-        <v>4447.5016721731517</v>
+        <v>4261.8658202494007</v>
       </c>
       <c r="K7" s="10"/>
       <c r="L7" s="10"/>
@@ -1972,93 +1997,99 @@
       <c r="V7" s="10"/>
       <c r="W7" s="10">
         <f>W36/Main!$D$13</f>
-        <v>8825.5073831838708</v>
-      </c>
-      <c r="X7" s="10"/>
+        <v>8457.1363959423652</v>
+      </c>
+      <c r="X7" s="10">
+        <f>X36/Main!$D$13</f>
+        <v>7464.6636945144401</v>
+      </c>
       <c r="Y7" s="10"/>
       <c r="Z7" s="10"/>
       <c r="AA7" s="10">
         <f>AA36/Main!$D$13</f>
-        <v>7862.8615737306991</v>
-      </c>
-      <c r="AB7" s="10"/>
+        <v>7534.67080183498</v>
+      </c>
+      <c r="AB7" s="10">
+        <f>AB36/Main!$D$13</f>
+        <v>5424.5073334625567</v>
+      </c>
       <c r="AC7" s="10"/>
       <c r="AD7" s="10"/>
       <c r="AF7" s="10">
         <f>AF36/Main!$D$13</f>
-        <v>13447.319803115097</v>
+        <v>12886.037345738838</v>
       </c>
       <c r="AG7" s="10">
         <f>AG36/Main!$D$13</f>
-        <v>16181.390331063312</v>
+        <v>15505.989532855203</v>
       </c>
       <c r="AH7" s="10">
         <f>AH36/Main!$D$13</f>
-        <v>16637.752005933518</v>
+        <v>15943.302965691024</v>
       </c>
       <c r="AI7" s="10">
         <f>AI36/Main!$D$13</f>
-        <v>16177.135729215832</v>
+        <v>15501.91251534535</v>
       </c>
       <c r="AJ7" s="10">
         <f>AJ36/Main!$D$13</f>
-        <v>14818.61641157036</v>
+        <v>14200.096918007364</v>
       </c>
       <c r="AK7" s="10">
         <f>AK36/Main!$D$13</f>
-        <v>20198.880722810329</v>
+        <v>19355.792466240226</v>
       </c>
       <c r="AL7" s="10">
         <f>AL36/Main!$D$13</f>
-        <v>18373.852066617219</v>
+        <v>17606.939329327386</v>
       </c>
       <c r="AM7" s="10">
         <f>AM36/Main!$D$13</f>
-        <v>36092.879778841612</v>
+        <v>34586.386250565352</v>
       </c>
       <c r="AN7" s="10">
         <f>AN36/Main!$D$13</f>
-        <v>32334.879643988941</v>
+        <v>30985.242618078439</v>
       </c>
       <c r="AO7" s="10">
         <f t="shared" ref="AO7:AS7" si="16">AO5-AO6</f>
-        <v>31110.185897107403</v>
+        <v>23355.871468630867</v>
       </c>
       <c r="AP7" s="10">
         <f t="shared" si="16"/>
-        <v>32061.302098361542</v>
+        <v>24138.172786353945</v>
       </c>
       <c r="AQ7" s="10">
         <f t="shared" si="16"/>
-        <v>32381.915119345154</v>
+        <v>27704.934688620269</v>
       </c>
       <c r="AR7" s="10">
         <f t="shared" si="16"/>
-        <v>32705.734270538596</v>
+        <v>31340.618011653296</v>
       </c>
       <c r="AS7" s="10">
         <f t="shared" si="16"/>
-        <v>33032.791613243986</v>
+        <v>31654.024191769829</v>
       </c>
       <c r="AT7" s="10">
         <f t="shared" ref="AT7:AX7" si="17">AT5-AT6</f>
-        <v>33363.119529376432</v>
+        <v>31970.564433687534</v>
       </c>
       <c r="AU7" s="10">
         <f t="shared" si="17"/>
-        <v>33696.750724670215</v>
+        <v>32290.270078024412</v>
       </c>
       <c r="AV7" s="10">
         <f t="shared" si="17"/>
-        <v>34033.718231916908</v>
+        <v>32613.172778804663</v>
       </c>
       <c r="AW7" s="10">
         <f t="shared" si="17"/>
-        <v>34374.055414236092</v>
+        <v>32939.304506592707</v>
       </c>
       <c r="AX7" s="10">
         <f t="shared" si="17"/>
-        <v>34717.79596837845</v>
+        <v>33268.697551658639</v>
       </c>
     </row>
     <row r="8" spans="2:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2067,31 +2098,31 @@
       </c>
       <c r="C8" s="5">
         <f>C37/Main!$D$13</f>
-        <v>-706.25042141460449</v>
+        <v>-676.77198423467075</v>
       </c>
       <c r="D8" s="5">
         <f>D37/Main!$D$13</f>
-        <v>-641.3728002157643</v>
+        <v>-614.60231310977576</v>
       </c>
       <c r="E8" s="5">
         <f>E37/Main!$D$13</f>
-        <v>-511.3343672038298</v>
+        <v>-489.9916004393616</v>
       </c>
       <c r="F8" s="5">
         <f>F37/Main!$D$13</f>
-        <v>-232.92428022385545</v>
+        <v>-223.20217096336498</v>
       </c>
       <c r="G8" s="5">
         <f>G37/Main!$D$13</f>
-        <v>84.768390533342327</v>
+        <v>81.230212573496146</v>
       </c>
       <c r="H8" s="5">
         <f>H37/Main!$D$13</f>
-        <v>-599.83817679185483</v>
+        <v>-574.80131808490012</v>
       </c>
       <c r="I8" s="5">
         <f>I37/Main!$D$13</f>
-        <v>-843.39559031757801</v>
+        <v>-808.19280222265297</v>
       </c>
       <c r="J8" s="5">
         <v>-300</v>
@@ -2110,16 +2141,22 @@
       <c r="V8" s="5"/>
       <c r="W8" s="5">
         <f>W37/Main!$D$13</f>
-        <v>-1112.1097700761918</v>
-      </c>
-      <c r="X8" s="5"/>
+        <v>-1065.6910253925178</v>
+      </c>
+      <c r="X8" s="5">
+        <f>X37/Main!$D$13</f>
+        <v>-642.10118239968983</v>
+      </c>
       <c r="Y8" s="5"/>
       <c r="Z8" s="5"/>
       <c r="AA8" s="5">
         <f>AA37/Main!$D$13</f>
-        <v>-951.00802373407055</v>
-      </c>
-      <c r="AB8" s="5"/>
+        <v>-911.3135620598307</v>
+      </c>
+      <c r="AB8" s="5">
+        <f>AB37/Main!$D$13</f>
+        <v>-850.16476061252172</v>
+      </c>
       <c r="AC8" s="5"/>
       <c r="AD8" s="5"/>
       <c r="AF8" s="10"/>
@@ -2127,67 +2164,67 @@
       <c r="AH8" s="10"/>
       <c r="AI8" s="5">
         <f>AI37/Main!$D$13</f>
-        <v>-2091.8818690580542</v>
+        <v>-2004.5680687471731</v>
       </c>
       <c r="AJ8" s="5">
         <f>AJ37/Main!$D$13</f>
-        <v>-2366.8599554986176</v>
+        <v>-2268.0687471732244</v>
       </c>
       <c r="AK8" s="5">
         <f>AK37/Main!$D$13</f>
-        <v>-3778.2078079697931</v>
+        <v>-3620.5078503585964</v>
       </c>
       <c r="AL8" s="5">
         <f>AL37/Main!$D$13</f>
-        <v>-4335.9382374755578</v>
+        <v>-4154.9589713768819</v>
       </c>
       <c r="AM8" s="5">
         <f>AM37/Main!$D$13</f>
-        <v>-5145.5532330928463</v>
+        <v>-4930.7811591393674</v>
       </c>
       <c r="AN8" s="5">
         <f>AN37/Main!$D$13</f>
-        <v>-3986.3731373474479</v>
+        <v>-3819.9844931188213</v>
       </c>
       <c r="AO8" s="5">
         <f t="shared" ref="AO8:AS8" si="18">AN8*1.02</f>
-        <v>-4066.1006000943971</v>
+        <v>-3896.3841829811977</v>
       </c>
       <c r="AP8" s="5">
         <f t="shared" si="18"/>
-        <v>-4147.4226120962849</v>
+        <v>-3974.3118666408218</v>
       </c>
       <c r="AQ8" s="5">
         <f t="shared" si="18"/>
-        <v>-4230.371064338211</v>
+        <v>-4053.7981039736383</v>
       </c>
       <c r="AR8" s="5">
         <f t="shared" si="18"/>
-        <v>-4314.9784856249753</v>
+        <v>-4134.8740660531112</v>
       </c>
       <c r="AS8" s="5">
         <f t="shared" si="18"/>
-        <v>-4401.2780553374751</v>
+        <v>-4217.5715473741739</v>
       </c>
       <c r="AT8" s="5">
         <f t="shared" ref="AT8:AT12" si="19">AS8*1.02</f>
-        <v>-4489.3036164442246</v>
+        <v>-4301.9229783216579</v>
       </c>
       <c r="AU8" s="5">
         <f t="shared" ref="AU8:AU12" si="20">AT8*1.02</f>
-        <v>-4579.0896887731096</v>
+        <v>-4387.9614378880915</v>
       </c>
       <c r="AV8" s="5">
         <f t="shared" ref="AV8:AV12" si="21">AU8*1.02</f>
-        <v>-4670.6714825485715</v>
+        <v>-4475.7206666458533</v>
       </c>
       <c r="AW8" s="5">
         <f t="shared" ref="AW8:AW12" si="22">AV8*1.02</f>
-        <v>-4764.0849121995434</v>
+        <v>-4565.23507997877</v>
       </c>
       <c r="AX8" s="5">
         <f t="shared" ref="AX8:AX12" si="23">AW8*1.02</f>
-        <v>-4859.3666104435342</v>
+        <v>-4656.5397815783454</v>
       </c>
     </row>
     <row r="9" spans="2:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2196,31 +2233,31 @@
       </c>
       <c r="C9" s="5">
         <f>C38/Main!$D$13</f>
-        <v>-522.89798395253183</v>
+        <v>-501.07255928151449</v>
       </c>
       <c r="D9" s="5">
         <f>D38/Main!$D$13</f>
-        <v>-432.55343537185627</v>
+        <v>-414.49893390191897</v>
       </c>
       <c r="E9" s="5">
         <f>E38/Main!$D$13</f>
-        <v>-411.92771896702851</v>
+        <v>-394.73412159979324</v>
       </c>
       <c r="F9" s="5">
         <f>F38/Main!$D$13</f>
-        <v>-694.82839997302949</v>
+        <v>-665.82671060282996</v>
       </c>
       <c r="G9" s="5">
         <f>G38/Main!$D$13</f>
-        <v>-773.98017665700218</v>
+        <v>-741.67474316728044</v>
       </c>
       <c r="H9" s="5">
         <f>H38/Main!$D$13</f>
-        <v>-358.60697188321757</v>
+        <v>-343.63894811656002</v>
       </c>
       <c r="I9" s="5">
         <f>I38/Main!$D$13</f>
-        <v>-356.54372597936754</v>
+        <v>-341.66182076629838</v>
       </c>
       <c r="J9" s="5">
         <v>-300</v>
@@ -2239,16 +2276,22 @@
       <c r="V9" s="5"/>
       <c r="W9" s="5">
         <f>W38/Main!$D$13</f>
-        <v>-1171.8697323174431</v>
-      </c>
-      <c r="X9" s="5"/>
+        <v>-1122.9566453447051</v>
+      </c>
+      <c r="X9" s="5">
+        <f>X38/Main!$D$13</f>
+        <v>-627.67332170317241</v>
+      </c>
       <c r="Y9" s="5"/>
       <c r="Z9" s="5"/>
       <c r="AA9" s="5">
         <f>AA38/Main!$D$13</f>
-        <v>-1036.4843908030477</v>
-      </c>
-      <c r="AB9" s="5"/>
+        <v>-993.22220068488718</v>
+      </c>
+      <c r="AB9" s="5">
+        <f>AB38/Main!$D$13</f>
+        <v>-898.26839826839819</v>
+      </c>
       <c r="AC9" s="5"/>
       <c r="AD9" s="5"/>
       <c r="AF9" s="10"/>
@@ -2256,67 +2299,67 @@
       <c r="AH9" s="10"/>
       <c r="AI9" s="5">
         <f>AI38/Main!$D$13</f>
-        <v>-2062.2075382644462</v>
+        <v>-1976.1323253860567</v>
       </c>
       <c r="AJ9" s="5">
         <f>AJ38/Main!$D$13</f>
-        <v>-2934.5897107410156</v>
+        <v>-2812.1018285197388</v>
       </c>
       <c r="AK9" s="5">
         <f>AK38/Main!$D$13</f>
-        <v>-2257.1640482772573</v>
+        <v>-2162.9514763843122</v>
       </c>
       <c r="AL9" s="5">
         <f>AL38/Main!$D$13</f>
-        <v>-2557.8180837435102</v>
+        <v>-2451.0564062802869</v>
       </c>
       <c r="AM9" s="5">
         <f>AM38/Main!$D$13</f>
-        <v>-5038.3386150630431</v>
+        <v>-4828.0416101311621</v>
       </c>
       <c r="AN9" s="5">
         <f>AN38/Main!$D$13</f>
-        <v>-3753.624165599083</v>
+        <v>-3596.9503133682238</v>
       </c>
       <c r="AO9" s="5">
         <f t="shared" ref="AO9:AS9" si="24">AN9*1.02</f>
-        <v>-3828.6966489110646</v>
+        <v>-3668.8893196355884</v>
       </c>
       <c r="AP9" s="5">
         <f t="shared" si="24"/>
-        <v>-3905.2705818892859</v>
+        <v>-3742.2671060283001</v>
       </c>
       <c r="AQ9" s="5">
         <f t="shared" si="24"/>
-        <v>-3983.3759935270718</v>
+        <v>-3817.112448148866</v>
       </c>
       <c r="AR9" s="5">
         <f t="shared" si="24"/>
-        <v>-4063.0435133976134</v>
+        <v>-3893.4546971118434</v>
       </c>
       <c r="AS9" s="5">
         <f t="shared" si="24"/>
-        <v>-4144.3043836655661</v>
+        <v>-3971.3237910540802</v>
       </c>
       <c r="AT9" s="5">
         <f t="shared" si="19"/>
-        <v>-4227.1904713388776</v>
+        <v>-4050.7502668751617</v>
       </c>
       <c r="AU9" s="5">
         <f t="shared" si="20"/>
-        <v>-4311.7342807656551</v>
+        <v>-4131.765272212665</v>
       </c>
       <c r="AV9" s="5">
         <f t="shared" si="21"/>
-        <v>-4397.9689663809686</v>
+        <v>-4214.4005776569184</v>
       </c>
       <c r="AW9" s="5">
         <f t="shared" si="22"/>
-        <v>-4485.9283457085885</v>
+        <v>-4298.6885892100572</v>
       </c>
       <c r="AX9" s="5">
         <f t="shared" si="23"/>
-        <v>-4575.6469126227603</v>
+        <v>-4384.6623609942581</v>
       </c>
     </row>
     <row r="10" spans="2:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2325,31 +2368,31 @@
       </c>
       <c r="C10" s="5">
         <f>C39/Main!$D$13</f>
-        <v>66.361000606837024</v>
+        <v>63.591135232926277</v>
       </c>
       <c r="D10" s="5">
         <f>D39/Main!$D$13</f>
-        <v>85.678646079158511</v>
+        <v>82.10247463978807</v>
       </c>
       <c r="E10" s="5">
         <f>E39/Main!$D$13</f>
-        <v>79.906951655316561</v>
+        <v>76.571687019448206</v>
       </c>
       <c r="F10" s="5">
         <f>F39/Main!$D$13</f>
-        <v>86.002292495448728</v>
+        <v>82.412612263358525</v>
       </c>
       <c r="G10" s="5">
         <f>G39/Main!$D$13</f>
-        <v>67.50724833119817</v>
+        <v>64.689539316404989</v>
       </c>
       <c r="H10" s="5">
         <f>H39/Main!$D$13</f>
-        <v>89.171330321623628</v>
+        <v>85.449376494152602</v>
       </c>
       <c r="I10" s="5">
         <f>I39/Main!$D$13</f>
-        <v>66.47562537927314</v>
+        <v>63.700975641274141</v>
       </c>
       <c r="J10" s="5">
         <v>93</v>
@@ -2368,16 +2411,22 @@
       <c r="V10" s="5"/>
       <c r="W10" s="5">
         <f>W39/Main!$D$13</f>
-        <v>111.31413930281168</v>
-      </c>
-      <c r="X10" s="5"/>
+        <v>106.66795890676487</v>
+      </c>
+      <c r="X10" s="5">
+        <f>X39/Main!$D$13</f>
+        <v>240.25974025974025</v>
+      </c>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5"/>
       <c r="AA10" s="5">
         <f>AA39/Main!$D$13</f>
-        <v>41.878497741217721</v>
-      </c>
-      <c r="AB10" s="5"/>
+        <v>40.130516249919232</v>
+      </c>
+      <c r="AB10" s="5">
+        <f>AB39/Main!$D$13</f>
+        <v>121.4641080312722</v>
+      </c>
       <c r="AC10" s="5"/>
       <c r="AD10" s="5"/>
       <c r="AF10" s="10"/>
@@ -2385,67 +2434,67 @@
       <c r="AH10" s="10"/>
       <c r="AI10" s="5">
         <f>AI39/Main!$D$13</f>
-        <v>317.94889083676082</v>
+        <v>304.67790915552109</v>
       </c>
       <c r="AJ10" s="5">
         <f>AJ39/Main!$D$13</f>
-        <v>320.52457689973704</v>
+        <v>307.14608774310267</v>
       </c>
       <c r="AK10" s="5">
         <f>AK39/Main!$D$13</f>
-        <v>296.65565369833456</v>
+        <v>284.27343800478127</v>
       </c>
       <c r="AL10" s="5">
         <f>AL39/Main!$D$13</f>
-        <v>830.10585934866162</v>
+        <v>795.45777605479088</v>
       </c>
       <c r="AM10" s="5">
         <f>AM39/Main!$D$13</f>
-        <v>699.27179556334704</v>
+        <v>670.08464172643278</v>
       </c>
       <c r="AN10" s="5">
         <f>AN39/Main!$D$13</f>
-        <v>1285.8944103566853</v>
+        <v>1232.2220068488725</v>
       </c>
       <c r="AO10" s="5">
         <f t="shared" ref="AO10:AS10" si="25">AN10*1.02</f>
-        <v>1311.612298563819</v>
+        <v>1256.86644698585</v>
       </c>
       <c r="AP10" s="5">
         <f t="shared" si="25"/>
-        <v>1337.8445445350953</v>
+        <v>1282.003775925567</v>
       </c>
       <c r="AQ10" s="5">
         <f t="shared" si="25"/>
-        <v>1364.6014354257973</v>
+        <v>1307.6438514440783</v>
       </c>
       <c r="AR10" s="5">
         <f t="shared" si="25"/>
-        <v>1391.8934641343133</v>
+        <v>1333.79672847296</v>
       </c>
       <c r="AS10" s="5">
         <f t="shared" si="25"/>
-        <v>1419.7313334169996</v>
+        <v>1360.4726630424193</v>
       </c>
       <c r="AT10" s="5">
         <f t="shared" si="19"/>
-        <v>1448.1259600853396</v>
+        <v>1387.6821163032678</v>
       </c>
       <c r="AU10" s="5">
         <f t="shared" si="20"/>
-        <v>1477.0884792870463</v>
+        <v>1415.4357586293331</v>
       </c>
       <c r="AV10" s="5">
         <f t="shared" si="21"/>
-        <v>1506.6302488727872</v>
+        <v>1443.7444738019199</v>
       </c>
       <c r="AW10" s="5">
         <f t="shared" si="22"/>
-        <v>1536.7628538502429</v>
+        <v>1472.6193632779582</v>
       </c>
       <c r="AX10" s="5">
         <f t="shared" si="23"/>
-        <v>1567.4981109272478</v>
+        <v>1502.0717505435173</v>
       </c>
     </row>
     <row r="11" spans="2:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2454,31 +2503,31 @@
       </c>
       <c r="C11" s="5">
         <f>C40/Main!$D$13</f>
-        <v>425.19047940125415</v>
+        <v>407.44330296569098</v>
       </c>
       <c r="D11" s="5">
         <f>D40/Main!$D$13</f>
-        <v>136.55181713977478</v>
+        <v>130.85223234476965</v>
       </c>
       <c r="E11" s="5">
         <f>E40/Main!$D$13</f>
-        <v>-177.50657406783088</v>
+        <v>-170.09756412741487</v>
       </c>
       <c r="F11" s="5">
         <f>F40/Main!$D$13</f>
-        <v>253.74553300519182</v>
+        <v>243.1543580797312</v>
       </c>
       <c r="G11" s="5">
         <f>G40/Main!$D$13</f>
-        <v>-57.379812554783896</v>
+        <v>-54.984816178846025</v>
       </c>
       <c r="H11" s="5">
         <f>H40/Main!$D$13</f>
-        <v>139.53880385678647</v>
+        <v>133.71454416230534</v>
       </c>
       <c r="I11" s="5">
         <f>I40/Main!$D$13</f>
-        <v>4.1939181444272133</v>
+        <v>4.0188667054338696</v>
       </c>
       <c r="J11" s="5">
         <v>50</v>
@@ -2497,16 +2546,22 @@
       <c r="V11" s="5"/>
       <c r="W11" s="5">
         <f>W40/Main!$D$13</f>
-        <v>-1597.9974377992044</v>
-      </c>
-      <c r="X11" s="5"/>
+        <v>-1531.298055178652</v>
+      </c>
+      <c r="X11" s="5">
+        <f>X40/Main!$D$13</f>
+        <v>2996.7693997544743</v>
+      </c>
       <c r="Y11" s="5"/>
       <c r="Z11" s="5"/>
       <c r="AA11" s="5">
         <f>AA40/Main!$D$13</f>
-        <v>1431.9668262423302</v>
-      </c>
-      <c r="AB11" s="5"/>
+        <v>1372.1974542870064</v>
+      </c>
+      <c r="AB11" s="5">
+        <f>AB40/Main!$D$13</f>
+        <v>-1031.1300639658848</v>
+      </c>
       <c r="AC11" s="5"/>
       <c r="AD11" s="5"/>
       <c r="AF11" s="10"/>
@@ -2514,67 +2569,67 @@
       <c r="AH11" s="10"/>
       <c r="AI11" s="5">
         <f>AI40/Main!$D$13</f>
-        <v>637.98125547838981</v>
+        <v>611.35232926277695</v>
       </c>
       <c r="AJ11" s="5">
         <f>AJ40/Main!$D$13</f>
-        <v>-102.09695907221361</v>
+        <v>-97.835497835497833</v>
       </c>
       <c r="AK11" s="5">
         <f>AK40/Main!$D$13</f>
-        <v>-1457.6697458027106</v>
+        <v>-1396.8275505588938</v>
       </c>
       <c r="AL11" s="5">
         <f>AL40/Main!$D$13</f>
-        <v>-839.56577439147725</v>
+        <v>-804.52284034373577</v>
       </c>
       <c r="AM11" s="5">
         <f>AM40/Main!$D$13</f>
-        <v>-1264.7023127233497</v>
+        <v>-1211.9144537054983</v>
       </c>
       <c r="AN11" s="5">
         <f>AN40/Main!$D$13</f>
-        <v>-4755.5255882947877</v>
+        <v>-4557.0330167345091</v>
       </c>
       <c r="AO11" s="5">
         <f t="shared" ref="AO11:AS11" si="26">AN11*1.02</f>
-        <v>-4850.6361000606839</v>
+        <v>-4648.1736770691996</v>
       </c>
       <c r="AP11" s="5">
         <f t="shared" si="26"/>
-        <v>-4947.6488220618976</v>
+        <v>-4741.1371506105834</v>
       </c>
       <c r="AQ11" s="5">
         <f t="shared" si="26"/>
-        <v>-5046.6017985031358</v>
+        <v>-4835.9598936227949</v>
       </c>
       <c r="AR11" s="5">
         <f t="shared" si="26"/>
-        <v>-5147.533834473199</v>
+        <v>-4932.6790914952508</v>
       </c>
       <c r="AS11" s="5">
         <f t="shared" si="26"/>
-        <v>-5250.4845111626628</v>
+        <v>-5031.3326733251561</v>
       </c>
       <c r="AT11" s="5">
         <f t="shared" si="19"/>
-        <v>-5355.4942013859163</v>
+        <v>-5131.9593267916589</v>
       </c>
       <c r="AU11" s="5">
         <f t="shared" si="20"/>
-        <v>-5462.6040854136345</v>
+        <v>-5234.5985133274926</v>
       </c>
       <c r="AV11" s="5">
         <f t="shared" si="21"/>
-        <v>-5571.8561671219077</v>
+        <v>-5339.2904835940426</v>
       </c>
       <c r="AW11" s="5">
         <f t="shared" si="22"/>
-        <v>-5683.2932904643458</v>
+        <v>-5446.0762932659236</v>
       </c>
       <c r="AX11" s="5">
         <f t="shared" si="23"/>
-        <v>-5796.9591562736332</v>
+        <v>-5554.9978191312421</v>
       </c>
     </row>
     <row r="12" spans="2:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2583,31 +2638,31 @@
       </c>
       <c r="C12" s="5">
         <f>C41/Main!$D$13</f>
-        <v>-6.6077809992583099</v>
+        <v>-6.3319764812302122</v>
       </c>
       <c r="D12" s="5">
         <f>D41/Main!$D$13</f>
-        <v>94.983480547501856</v>
+        <v>91.018931317438771</v>
       </c>
       <c r="E12" s="5">
         <f>E41/Main!$D$13</f>
-        <v>131.879172004585</v>
+        <v>126.37462040447114</v>
       </c>
       <c r="F12" s="5">
         <f>F41/Main!$D$13</f>
-        <v>323.24860090351291</v>
+        <v>309.75641274148734</v>
       </c>
       <c r="G12" s="5">
         <f>G41/Main!$D$13</f>
-        <v>-24.266738588092508</v>
+        <v>-23.253860567293401</v>
       </c>
       <c r="H12" s="5">
         <f>H41/Main!$D$13</f>
-        <v>24.988200391072752</v>
+        <v>23.945209019835882</v>
       </c>
       <c r="I12" s="5">
         <f>I41/Main!$D$13</f>
-        <v>96.075787202481294</v>
+        <v>92.065645796989074</v>
       </c>
       <c r="J12" s="5">
         <v>0</v>
@@ -2626,16 +2681,22 @@
       <c r="V12" s="5"/>
       <c r="W12" s="5">
         <f>W41/Main!$D$13</f>
-        <v>-30.813835884296406</v>
-      </c>
-      <c r="X12" s="5"/>
+        <v>-29.527686244104153</v>
+      </c>
+      <c r="X12" s="5">
+        <f>X41/Main!$D$13</f>
+        <v>-55.094656587193896</v>
+      </c>
       <c r="Y12" s="5"/>
       <c r="Z12" s="5"/>
       <c r="AA12" s="5">
         <f>AA41/Main!$D$13</f>
-        <v>-66.2935742701099</v>
-      </c>
-      <c r="AB12" s="5"/>
+        <v>-63.526523228015762</v>
+      </c>
+      <c r="AB12" s="5">
+        <f>AB41/Main!$D$13</f>
+        <v>161.33617626154938</v>
+      </c>
       <c r="AC12" s="5"/>
       <c r="AD12" s="5"/>
       <c r="AF12" s="10"/>
@@ -2643,67 +2704,67 @@
       <c r="AH12" s="10"/>
       <c r="AI12" s="5">
         <f>AI41/Main!$D$13</f>
-        <v>543.50347245634146</v>
+        <v>520.8179879821671</v>
       </c>
       <c r="AJ12" s="5">
         <f>AJ41/Main!$D$13</f>
-        <v>129.8428966354258</v>
+        <v>124.42333785617367</v>
       </c>
       <c r="AK12" s="5">
         <f>AK41/Main!$D$13</f>
-        <v>488.57797855842489</v>
+        <v>468.18504878206369</v>
       </c>
       <c r="AL12" s="5">
         <f>AL41/Main!$D$13</f>
-        <v>526.66037354190541</v>
+        <v>504.67790915552104</v>
       </c>
       <c r="AM12" s="5">
         <f>AM41/Main!$D$13</f>
-        <v>-120.81451014766368</v>
+        <v>-115.77179039865607</v>
       </c>
       <c r="AN12" s="5">
         <f>AN41/Main!$D$13</f>
-        <v>293.28433686197826</v>
+        <v>281.04283775925563</v>
       </c>
       <c r="AO12" s="5">
         <f t="shared" ref="AO12:AS12" si="27">AN12*1.02</f>
-        <v>299.15002359921783</v>
+        <v>286.66369451444075</v>
       </c>
       <c r="AP12" s="5">
         <f t="shared" si="27"/>
-        <v>305.13302407120221</v>
+        <v>292.39696840472959</v>
       </c>
       <c r="AQ12" s="5">
         <f t="shared" si="27"/>
-        <v>311.23568455262625</v>
+        <v>298.24490777282421</v>
       </c>
       <c r="AR12" s="5">
         <f t="shared" si="27"/>
-        <v>317.46039824367881</v>
+        <v>304.20980592828067</v>
       </c>
       <c r="AS12" s="5">
         <f t="shared" si="27"/>
-        <v>323.8096062085524</v>
+        <v>310.29400204684629</v>
       </c>
       <c r="AT12" s="5">
         <f t="shared" si="19"/>
-        <v>330.28579833272346</v>
+        <v>316.49988208778319</v>
       </c>
       <c r="AU12" s="5">
         <f t="shared" si="20"/>
-        <v>336.89151429937795</v>
+        <v>322.82987972953885</v>
       </c>
       <c r="AV12" s="5">
         <f t="shared" si="21"/>
-        <v>343.62934458536552</v>
+        <v>329.28647732412963</v>
       </c>
       <c r="AW12" s="5">
         <f t="shared" si="22"/>
-        <v>350.50193147707284</v>
+        <v>335.87220687061222</v>
       </c>
       <c r="AX12" s="5">
         <f t="shared" si="23"/>
-        <v>357.51197010661429</v>
+        <v>342.58965100802448</v>
       </c>
     </row>
     <row r="13" spans="2:50" x14ac:dyDescent="0.3">
@@ -2712,31 +2773,31 @@
       </c>
       <c r="C13" s="5">
         <f>C42/Main!$D$13</f>
-        <v>-744.2047063583035</v>
+        <v>-713.14208179879813</v>
       </c>
       <c r="D13" s="5">
         <f>D42/Main!$D$13</f>
-        <v>-756.71229182118532</v>
+        <v>-725.12760870969817</v>
       </c>
       <c r="E13" s="5">
         <f>E42/Main!$D$13</f>
-        <v>-888.98253657878763</v>
+        <v>-851.87697874265029</v>
       </c>
       <c r="F13" s="5">
         <f>F42/Main!$D$13</f>
-        <v>-264.75625379273146</v>
+        <v>-253.70549848161787</v>
       </c>
       <c r="G13" s="5">
         <f>G42/Main!$D$13</f>
-        <v>-703.35108893533811</v>
+        <v>-673.99366802351869</v>
       </c>
       <c r="H13" s="5">
         <f>H42/Main!$D$13</f>
-        <v>-704.74681410558958</v>
+        <v>-675.33113652516636</v>
       </c>
       <c r="I13" s="5">
         <f>I42/Main!$D$13</f>
-        <v>-1033.193985570764</v>
+        <v>-990.06913484525421</v>
       </c>
       <c r="J13" s="5">
         <f>SUM(J8:J12)</f>
@@ -2756,93 +2817,99 @@
       <c r="V13" s="5"/>
       <c r="W13" s="5">
         <f>W42/Main!$D$13</f>
-        <v>-3801.4766367743241</v>
-      </c>
-      <c r="X13" s="5"/>
+        <v>-3642.8054532532142</v>
+      </c>
+      <c r="X13" s="5">
+        <f>X42/Main!$D$13</f>
+        <v>1912.1599793241583</v>
+      </c>
       <c r="Y13" s="5"/>
       <c r="Z13" s="5"/>
       <c r="AA13" s="5">
         <f>AA42/Main!$D$13</f>
-        <v>-579.94066482368009</v>
-      </c>
-      <c r="AB13" s="5"/>
+        <v>-555.73431543580796</v>
+      </c>
+      <c r="AB13" s="5">
+        <f>AB42/Main!$D$13</f>
+        <v>-2496.7629385539831</v>
+      </c>
       <c r="AC13" s="5"/>
       <c r="AD13" s="5"/>
       <c r="AF13" s="5">
         <f>AF42/Main!$D$13</f>
-        <v>-1344.8385139235386</v>
+        <v>-1288.7058215416423</v>
       </c>
       <c r="AG13" s="5">
         <f>AG42/Main!$D$13</f>
-        <v>-1487.2024812891916</v>
+        <v>-1425.1276087096983</v>
       </c>
       <c r="AH13" s="5">
         <f>AH42/Main!$D$13</f>
-        <v>1227.6987391275031</v>
+        <v>1176.4553854106093</v>
       </c>
       <c r="AI13" s="5">
         <f>AI42/Main!$D$13</f>
-        <v>-2654.6557885510078</v>
+        <v>-2543.8521677327644</v>
       </c>
       <c r="AJ13" s="5">
         <f>AJ42/Main!$D$13</f>
-        <v>-4953.1791517766842</v>
+        <v>-4746.4366479291848</v>
       </c>
       <c r="AK13" s="5">
         <f>AK42/Main!$D$13</f>
-        <v>-6707.8079697930007</v>
+        <v>-6427.8283905149574</v>
       </c>
       <c r="AL13" s="5">
         <f>AL42/Main!$D$13</f>
-        <v>-6376.555862719978</v>
+        <v>-6110.402532790592</v>
       </c>
       <c r="AM13" s="5">
         <f>AM42/Main!$D$13</f>
-        <v>-10870.136875463555</v>
+        <v>-10416.424371648252</v>
       </c>
       <c r="AN13" s="5">
         <f>AN42/Main!$D$13</f>
-        <v>-10916.344144022654</v>
+        <v>-10460.702978613426</v>
       </c>
       <c r="AO13" s="5">
         <f t="shared" ref="AO13:AS13" si="28">SUM(AO8:AO12)</f>
-        <v>-11134.67102690311</v>
+        <v>-10669.917038185695</v>
       </c>
       <c r="AP13" s="5">
         <f t="shared" si="28"/>
-        <v>-11357.364447441172</v>
+        <v>-10883.31537894941</v>
       </c>
       <c r="AQ13" s="5">
         <f t="shared" si="28"/>
-        <v>-11584.511736389995</v>
+        <v>-11100.981686528397</v>
       </c>
       <c r="AR13" s="5">
         <f t="shared" si="28"/>
-        <v>-11816.201971117796</v>
+        <v>-11323.001320258965</v>
       </c>
       <c r="AS13" s="5">
         <f t="shared" si="28"/>
-        <v>-12052.52601054015</v>
+        <v>-11549.461346664144</v>
       </c>
       <c r="AT13" s="5">
         <f t="shared" ref="AT13:AX13" si="29">SUM(AT8:AT12)</f>
-        <v>-12293.576530750957</v>
+        <v>-11780.450573597429</v>
       </c>
       <c r="AU13" s="5">
         <f t="shared" si="29"/>
-        <v>-12539.448061365974</v>
+        <v>-12016.059585069375</v>
       </c>
       <c r="AV13" s="5">
         <f t="shared" si="29"/>
-        <v>-12790.237022593294</v>
+        <v>-12256.380776770766</v>
       </c>
       <c r="AW13" s="5">
         <f t="shared" si="29"/>
-        <v>-13046.041763045163</v>
+        <v>-12501.508392306181</v>
       </c>
       <c r="AX13" s="5">
         <f t="shared" si="29"/>
-        <v>-13306.962598306065</v>
+        <v>-12751.538560152305</v>
       </c>
     </row>
     <row r="14" spans="2:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2851,35 +2918,35 @@
       </c>
       <c r="C14" s="10">
         <f>C43/Main!$D$13</f>
-        <v>5737.8733733396266</v>
+        <v>5498.3782386767462</v>
       </c>
       <c r="D14" s="10">
         <f>D43/Main!$D$13</f>
-        <v>5197.4580271053874</v>
+        <v>4980.5194805194806</v>
       </c>
       <c r="E14" s="10">
         <f>E43/Main!$D$13</f>
-        <v>5204.9221225810797</v>
+        <v>4987.6720294630741</v>
       </c>
       <c r="F14" s="10">
         <f>F43/Main!$D$13</f>
-        <v>2691.5379947407455</v>
+        <v>2579.1949344188147</v>
       </c>
       <c r="G14" s="10">
         <f>G43/Main!$D$13</f>
-        <v>797.20854965949695</v>
+        <v>763.93357885895193</v>
       </c>
       <c r="H14" s="10">
         <f>H43/Main!$D$13</f>
-        <v>4116.9307531521808</v>
+        <v>3945.0927182270461</v>
       </c>
       <c r="I14" s="10">
         <f>I43/Main!$D$13</f>
-        <v>7694.5114961904119</v>
+        <v>7373.3475479744129</v>
       </c>
       <c r="J14" s="10">
         <f>J7-J13</f>
-        <v>4904.5016721731517</v>
+        <v>4718.8658202494007</v>
       </c>
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
@@ -2895,93 +2962,99 @@
       <c r="V14" s="10"/>
       <c r="W14" s="10">
         <f>W43/Main!$D$13</f>
-        <v>12626.984019958196</v>
-      </c>
-      <c r="X14" s="10"/>
+        <v>12099.94184919558</v>
+      </c>
+      <c r="X14" s="10">
+        <f>X43/Main!$D$13</f>
+        <v>5552.5037151902816</v>
+      </c>
       <c r="Y14" s="10"/>
       <c r="Z14" s="10"/>
       <c r="AA14" s="10">
         <f>AA43/Main!$D$13</f>
-        <v>8442.8022385543791</v>
-      </c>
-      <c r="AB14" s="10"/>
+        <v>8090.4051172707887</v>
+      </c>
+      <c r="AB14" s="10">
+        <f>AB43/Main!$D$13</f>
+        <v>7921.2702720165398</v>
+      </c>
       <c r="AC14" s="10"/>
       <c r="AD14" s="10"/>
       <c r="AF14" s="10">
         <f>AF43/Main!$D$13</f>
-        <v>14792.158317038635</v>
+        <v>14174.74316728048</v>
       </c>
       <c r="AG14" s="10">
         <f>AG43/Main!$D$13</f>
-        <v>17668.592812352505</v>
+        <v>16931.117141564901</v>
       </c>
       <c r="AH14" s="10">
         <f>AH43/Main!$D$13</f>
-        <v>15410.053266806015</v>
+        <v>14766.847580280415</v>
       </c>
       <c r="AI14" s="10">
         <f>AI43/Main!$D$13</f>
-        <v>18831.79151776684</v>
+        <v>18045.764683078116</v>
       </c>
       <c r="AJ14" s="10">
         <f>AJ43/Main!$D$13</f>
-        <v>19771.795563347045</v>
+        <v>18946.533565936548</v>
       </c>
       <c r="AK14" s="10">
         <f>AK43/Main!$D$13</f>
-        <v>26906.688692603329</v>
+        <v>25783.620856755184</v>
       </c>
       <c r="AL14" s="10">
         <f>AL43/Main!$D$13</f>
-        <v>24750.407929337198</v>
+        <v>23717.341862117981</v>
       </c>
       <c r="AM14" s="10">
         <f>AM43/Main!$D$13</f>
-        <v>46963.016654305167</v>
+        <v>45002.810622213605</v>
       </c>
       <c r="AN14" s="10">
         <f>AN43/Main!$D$13</f>
-        <v>43251.223788011594</v>
+        <v>41445.945596691861</v>
       </c>
       <c r="AO14" s="10">
         <f t="shared" ref="AO14:AS14" si="30">AO7-AO13</f>
-        <v>42244.856924010513</v>
+        <v>34025.788506816563</v>
       </c>
       <c r="AP14" s="10">
         <f t="shared" si="30"/>
-        <v>43418.666545802713</v>
+        <v>35021.488165303352</v>
       </c>
       <c r="AQ14" s="10">
         <f t="shared" si="30"/>
-        <v>43966.426855735146</v>
+        <v>38805.916375148663</v>
       </c>
       <c r="AR14" s="10">
         <f t="shared" si="30"/>
-        <v>44521.936241656396</v>
+        <v>42663.619331912261</v>
       </c>
       <c r="AS14" s="10">
         <f t="shared" si="30"/>
-        <v>45085.31762378414</v>
+        <v>43203.485538433975</v>
       </c>
       <c r="AT14" s="10">
         <f t="shared" ref="AT14:AX14" si="31">AT7-AT13</f>
-        <v>45656.69606012739</v>
+        <v>43751.015007284965</v>
       </c>
       <c r="AU14" s="10">
         <f t="shared" si="31"/>
-        <v>46236.198786036191</v>
+        <v>44306.329663093784</v>
       </c>
       <c r="AV14" s="10">
         <f t="shared" si="31"/>
-        <v>46823.955254510205</v>
+        <v>44869.553555575432</v>
       </c>
       <c r="AW14" s="10">
         <f t="shared" si="31"/>
-        <v>47420.097177281255</v>
+        <v>45440.81289889889</v>
       </c>
       <c r="AX14" s="10">
         <f t="shared" si="31"/>
-        <v>48024.758566684512</v>
+        <v>46020.23611181094</v>
       </c>
     </row>
     <row r="15" spans="2:50" x14ac:dyDescent="0.3">
@@ -2990,35 +3063,35 @@
       </c>
       <c r="C15" s="5">
         <f>C44/Main!$D$13</f>
-        <v>1480.7025824286966</v>
+        <v>1418.8990114363248</v>
       </c>
       <c r="D15" s="5">
         <f>D44/Main!$D$13</f>
-        <v>1471.4044905940259</v>
+        <v>1409.989015959165</v>
       </c>
       <c r="E15" s="5">
         <f>E44/Main!$D$13</f>
-        <v>1252.4307194390128</v>
+        <v>1200.1550688117852</v>
       </c>
       <c r="F15" s="5">
         <f>F44/Main!$D$13</f>
-        <v>392.70447036612501</v>
+        <v>376.31323899980612</v>
       </c>
       <c r="G15" s="5">
         <f>G44/Main!$D$13</f>
-        <v>-210.46456746004989</v>
+        <v>-201.6799121276733</v>
       </c>
       <c r="H15" s="5">
         <f>H44/Main!$D$13</f>
-        <v>868.72766502595914</v>
+        <v>832.46753246753246</v>
       </c>
       <c r="I15" s="5">
         <f>I44/Main!$D$13</f>
-        <v>1845.2295866765558</v>
+        <v>1768.2108935840279</v>
       </c>
       <c r="J15" s="5">
         <f>J14*0.24</f>
-        <v>1177.0804013215563</v>
+        <v>1132.5277968598562</v>
       </c>
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
@@ -3034,93 +3107,99 @@
       <c r="V15" s="5"/>
       <c r="W15" s="5">
         <f>W44/Main!$D$13</f>
-        <v>3428.1909513856112</v>
-      </c>
-      <c r="X15" s="5"/>
+        <v>3285.1004716676357</v>
+      </c>
+      <c r="X15" s="5">
+        <f>X44/Main!$D$13</f>
+        <v>2312.9999353879948</v>
+      </c>
       <c r="Y15" s="5"/>
       <c r="Z15" s="5"/>
       <c r="AA15" s="5">
         <f>AA44/Main!$D$13</f>
-        <v>2561.924347650192</v>
-      </c>
-      <c r="AB15" s="5"/>
+        <v>2454.9912773793371</v>
+      </c>
+      <c r="AB15" s="5">
+        <f>AB44/Main!$D$13</f>
+        <v>1634.9034050526586</v>
+      </c>
       <c r="AC15" s="5"/>
       <c r="AD15" s="5"/>
       <c r="AF15" s="5">
         <f>AF44/Main!$D$13</f>
-        <v>4240.4423167689301</v>
+        <v>4063.4489888221228</v>
       </c>
       <c r="AG15" s="5">
         <f>AG44/Main!$D$13</f>
-        <v>3401.0248803182521</v>
+        <v>3259.0682948891904</v>
       </c>
       <c r="AH15" s="5">
         <f>AH44/Main!$D$13</f>
-        <v>4449.7606365046186</v>
+        <v>4264.0304968663177</v>
       </c>
       <c r="AI15" s="5">
         <f>AI44/Main!$D$13</f>
-        <v>4597.2422628278609</v>
+        <v>4405.3563352070814</v>
       </c>
       <c r="AJ15" s="5">
         <f>AJ44/Main!$D$13</f>
-        <v>4382.5500640550199</v>
+        <v>4199.6252503715186</v>
       </c>
       <c r="AK15" s="5">
         <f>AK44/Main!$D$13</f>
-        <v>7524.2262827860559</v>
+        <v>7210.169929572914</v>
       </c>
       <c r="AL15" s="5">
         <f>AL44/Main!$D$13</f>
-        <v>7927.7526801968852</v>
+        <v>7596.8533953608576</v>
       </c>
       <c r="AM15" s="5">
         <f>AM44/Main!$D$13</f>
-        <v>12768.289393837233</v>
+        <v>12235.34922788654</v>
       </c>
       <c r="AN15" s="5">
         <f>AN44/Main!$D$13</f>
-        <v>10955.667183601914</v>
+        <v>10498.384699877237</v>
       </c>
       <c r="AO15" s="5">
         <f t="shared" ref="AO15:AS15" si="32">AO14*0.26</f>
-        <v>10983.662800242733</v>
+        <v>8846.7050117723065</v>
       </c>
       <c r="AP15" s="5">
         <f t="shared" si="32"/>
-        <v>11288.853301908706</v>
+        <v>9105.5869229788714</v>
       </c>
       <c r="AQ15" s="5">
         <f t="shared" si="32"/>
-        <v>11431.270982491138</v>
+        <v>10089.538257538652</v>
       </c>
       <c r="AR15" s="5">
         <f t="shared" si="32"/>
-        <v>11575.703422830664</v>
+        <v>11092.541026297189</v>
       </c>
       <c r="AS15" s="5">
         <f t="shared" si="32"/>
-        <v>11722.182582183877</v>
+        <v>11232.906239992833</v>
       </c>
       <c r="AT15" s="5">
         <f t="shared" ref="AT15:AX15" si="33">AT14*0.26</f>
-        <v>11870.740975633122</v>
+        <v>11375.263901894092</v>
       </c>
       <c r="AU15" s="5">
         <f t="shared" si="33"/>
-        <v>12021.41168436941</v>
+        <v>11519.645712404385</v>
       </c>
       <c r="AV15" s="5">
         <f t="shared" si="33"/>
-        <v>12174.228366172654</v>
+        <v>11666.083924449613</v>
       </c>
       <c r="AW15" s="5">
         <f t="shared" si="33"/>
-        <v>12329.225266093126</v>
+        <v>11814.611353713712</v>
       </c>
       <c r="AX15" s="5">
         <f t="shared" si="33"/>
-        <v>12486.437227337974</v>
+        <v>11965.261389070845</v>
       </c>
     </row>
     <row r="16" spans="2:50" x14ac:dyDescent="0.3">
@@ -3129,31 +3208,31 @@
       </c>
       <c r="C16" s="5">
         <f>C45/Main!$D$13</f>
-        <v>82.610747758074297</v>
+        <v>79.162628416359752</v>
       </c>
       <c r="D16" s="5">
         <f>D45/Main!$D$13</f>
-        <v>149.69321016789158</v>
+        <v>143.4451121018285</v>
       </c>
       <c r="E16" s="5">
         <f>E45/Main!$D$13</f>
-        <v>181.33638999393162</v>
+        <v>173.76752600633196</v>
       </c>
       <c r="F16" s="5">
         <f>F45/Main!$D$13</f>
-        <v>91.956038028453918</v>
+        <v>88.117852296956769</v>
       </c>
       <c r="G16" s="5">
         <f>G45/Main!$D$13</f>
-        <v>-63.353785988807225</v>
+        <v>-60.70943981391742</v>
       </c>
       <c r="H16" s="5">
         <f>H45/Main!$D$13</f>
-        <v>75.625379273144091</v>
+        <v>72.468824707630674</v>
       </c>
       <c r="I16" s="5">
         <f>I45/Main!$D$13</f>
-        <v>194.26876137819431</v>
+        <v>186.16010854816824</v>
       </c>
       <c r="J16" s="5">
         <v>300</v>
@@ -3172,93 +3251,99 @@
       <c r="V16" s="5"/>
       <c r="W16" s="5">
         <f>W45/Main!$D$13</f>
-        <v>205.48850380958802</v>
-      </c>
-      <c r="X16" s="5"/>
+        <v>196.91154616527749</v>
+      </c>
+      <c r="X16" s="5">
+        <f>X45/Main!$D$13</f>
+        <v>-464.8058409252439</v>
+      </c>
       <c r="Y16" s="5"/>
       <c r="Z16" s="5"/>
       <c r="AA16" s="5">
         <f>AA45/Main!$D$13</f>
-        <v>207.99676353583709</v>
-      </c>
-      <c r="AB16" s="5"/>
+        <v>199.31511274794855</v>
+      </c>
+      <c r="AB16" s="5">
+        <f>AB45/Main!$D$13</f>
+        <v>264.0111132648446</v>
+      </c>
       <c r="AC16" s="5"/>
       <c r="AD16" s="5"/>
       <c r="AF16" s="5">
         <f>AF45/Main!$D$13</f>
-        <v>-1794.7812015373204</v>
+        <v>-1719.8681915099824</v>
       </c>
       <c r="AG16" s="5">
         <f>AG45/Main!$D$13</f>
-        <v>-2548.4458229384395</v>
+        <v>-2442.0753375977256</v>
       </c>
       <c r="AH16" s="5">
         <f>AH45/Main!$D$13</f>
-        <v>-1735.230260939923</v>
+        <v>-1662.802868773018</v>
       </c>
       <c r="AI16" s="5">
         <f>AI45/Main!$D$13</f>
-        <v>505.59638594835144</v>
+        <v>484.49311882147703</v>
       </c>
       <c r="AJ16" s="5">
         <f>AJ45/Main!$D$13</f>
-        <v>250.27307666374486</v>
+        <v>239.8268398268398</v>
       </c>
       <c r="AK16" s="5">
         <f>AK45/Main!$D$13</f>
-        <v>165.22149551614859</v>
+        <v>158.3252568327195</v>
       </c>
       <c r="AL16" s="5">
         <f>AL45/Main!$D$13</f>
-        <v>280.83069246847816</v>
+        <v>269.10900045228402</v>
       </c>
       <c r="AM16" s="5">
         <f>AM45/Main!$D$13</f>
-        <v>852.86224799406648</v>
+        <v>817.26432771208886</v>
       </c>
       <c r="AN16" s="5">
         <f>AN45/Main!$D$13</f>
-        <v>166.34077270581889</v>
+        <v>159.39781611423402</v>
       </c>
       <c r="AO16" s="5">
         <f t="shared" ref="AO16:AS16" si="34">AN16*1.01</f>
-        <v>168.00418043287709</v>
+        <v>160.99179427537635</v>
       </c>
       <c r="AP16" s="5">
         <f t="shared" si="34"/>
-        <v>169.68422223720586</v>
+        <v>162.6017122181301</v>
       </c>
       <c r="AQ16" s="5">
         <f t="shared" si="34"/>
-        <v>171.38106445957791</v>
+        <v>164.22772934031141</v>
       </c>
       <c r="AR16" s="5">
         <f t="shared" si="34"/>
-        <v>173.0948751041737</v>
+        <v>165.87000663371452</v>
       </c>
       <c r="AS16" s="5">
         <f t="shared" si="34"/>
-        <v>174.82582385521545</v>
+        <v>167.52870670005166</v>
       </c>
       <c r="AT16" s="5">
         <f t="shared" ref="AT16" si="35">AS16*1.01</f>
-        <v>176.5740820937676</v>
+        <v>169.20399376705217</v>
       </c>
       <c r="AU16" s="5">
         <f t="shared" ref="AU16" si="36">AT16*1.01</f>
-        <v>178.33982291470528</v>
+        <v>170.8960337047227</v>
       </c>
       <c r="AV16" s="5">
         <f t="shared" ref="AV16" si="37">AU16*1.01</f>
-        <v>180.12322114385233</v>
+        <v>172.60499404176991</v>
       </c>
       <c r="AW16" s="5">
         <f t="shared" ref="AW16" si="38">AV16*1.01</f>
-        <v>181.92445335529086</v>
+        <v>174.33104398218762</v>
       </c>
       <c r="AX16" s="5">
         <f t="shared" ref="AX16" si="39">AW16*1.01</f>
-        <v>183.74369788884377</v>
+        <v>176.07435442200949</v>
       </c>
     </row>
     <row r="17" spans="2:139" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3267,35 +3352,35 @@
       </c>
       <c r="C17" s="10">
         <f>C46/Main!$D$13</f>
-        <v>4174.5600431528555</v>
+        <v>4000.3165988240612</v>
       </c>
       <c r="D17" s="10">
         <f>D46/Main!$D$13</f>
-        <v>3576.3603263434698</v>
+        <v>3427.0853524584863</v>
       </c>
       <c r="E17" s="10">
         <f>E46/Main!$D$13</f>
-        <v>3771.1550131481358</v>
+        <v>3613.7494346449566</v>
       </c>
       <c r="F17" s="10">
         <f>F46/Main!$D$13</f>
-        <v>2206.8774863461667</v>
+        <v>2114.7638431220521</v>
       </c>
       <c r="G17" s="10">
         <f>G46/Main!$D$13</f>
-        <v>1071.0269031083542</v>
+        <v>1026.3229308005427</v>
       </c>
       <c r="H17" s="10">
         <f>H46/Main!$D$13</f>
-        <v>3172.5777088530781</v>
+        <v>3040.1563610518833</v>
       </c>
       <c r="I17" s="10">
         <f>I46/Main!$D$13</f>
-        <v>5655.013148135662</v>
+        <v>5418.9765458422171</v>
       </c>
       <c r="J17" s="10">
         <f>J14-J15-J16</f>
-        <v>3427.4212708515952</v>
+        <v>3286.3380233895446</v>
       </c>
       <c r="K17" s="10"/>
       <c r="L17" s="10"/>
@@ -3311,449 +3396,455 @@
       <c r="V17" s="10"/>
       <c r="W17" s="10">
         <f>W46/Main!$D$13</f>
-        <v>8993.304564762997</v>
-      </c>
-      <c r="X17" s="10"/>
+        <v>8617.9298313626659</v>
+      </c>
+      <c r="X17" s="10">
+        <f>X46/Main!$D$13</f>
+        <v>3704.3096207275307</v>
+      </c>
       <c r="Y17" s="10"/>
       <c r="Z17" s="10"/>
       <c r="AA17" s="10">
         <f>AA46/Main!$D$13</f>
-        <v>5672.8811273683496</v>
-      </c>
-      <c r="AB17" s="10"/>
+        <v>5436.0987271435033</v>
+      </c>
+      <c r="AB17" s="10">
+        <f>AB46/Main!$D$13</f>
+        <v>6022.3557536990365</v>
+      </c>
       <c r="AC17" s="10"/>
       <c r="AD17" s="10"/>
       <c r="AF17" s="10">
         <f>AF46/Main!$D$13</f>
-        <v>12346.497201807026</v>
+        <v>11831.162369968339</v>
       </c>
       <c r="AG17" s="10">
         <f>AG46/Main!$D$13</f>
-        <v>16816.013754972693</v>
+        <v>16114.124184273436</v>
       </c>
       <c r="AH17" s="10">
         <f>AH46/Main!$D$13</f>
-        <v>12695.522891241319</v>
+        <v>12165.619952187115</v>
       </c>
       <c r="AI17" s="10">
         <f>AI46/Main!$D$13</f>
-        <v>13728.952868990627</v>
+        <v>13155.915229049557</v>
       </c>
       <c r="AJ17" s="10">
         <f>AJ46/Main!$D$13</f>
-        <v>15138.972422628278</v>
+        <v>14507.08147573819</v>
       </c>
       <c r="AK17" s="10">
         <f>AK46/Main!$D$13</f>
-        <v>19217.240914301125</v>
+        <v>18415.125670349549</v>
       </c>
       <c r="AL17" s="10">
         <f>AL46/Main!$D$13</f>
-        <v>16541.824556671836</v>
+        <v>15851.379466304839</v>
       </c>
       <c r="AM17" s="10">
         <f>AM46/Main!$D$13</f>
-        <v>33341.865012473871</v>
+        <v>31950.197066614975</v>
       </c>
       <c r="AN17" s="10">
         <f>AN46/Main!$D$13</f>
-        <v>32129.215831703863</v>
+        <v>30788.163080700393</v>
       </c>
       <c r="AO17" s="10">
         <f t="shared" ref="AO17:AS17" si="40">AO14-AO15-AO16</f>
-        <v>31093.189943334906</v>
+        <v>25018.091700768884</v>
       </c>
       <c r="AP17" s="10">
         <f t="shared" si="40"/>
-        <v>31960.129021656801</v>
+        <v>25753.299530106349</v>
       </c>
       <c r="AQ17" s="10">
         <f t="shared" si="40"/>
-        <v>32363.77480878443</v>
+        <v>28552.150388269696</v>
       </c>
       <c r="AR17" s="10">
         <f t="shared" si="40"/>
-        <v>32773.137943721558</v>
+        <v>31405.208298981357</v>
       </c>
       <c r="AS17" s="10">
         <f t="shared" si="40"/>
-        <v>33188.309217745045</v>
+        <v>31803.050591741092</v>
       </c>
       <c r="AT17" s="10">
         <f t="shared" ref="AT17:AX17" si="41">AT14-AT15-AT16</f>
-        <v>33609.381002400507</v>
+        <v>32206.547111623822</v>
       </c>
       <c r="AU17" s="10">
         <f t="shared" si="41"/>
-        <v>34036.447278752072</v>
+        <v>32615.787916984682</v>
       </c>
       <c r="AV17" s="10">
         <f t="shared" si="41"/>
-        <v>34469.603667193696</v>
+        <v>33030.864637084043</v>
       </c>
       <c r="AW17" s="10">
         <f t="shared" si="41"/>
-        <v>34908.947457832837</v>
+        <v>33451.87050120299</v>
       </c>
       <c r="AX17" s="10">
         <f t="shared" si="41"/>
-        <v>35354.577641457698</v>
+        <v>33878.900368318085</v>
       </c>
       <c r="AY17" s="1">
         <f t="shared" ref="AY17:CD17" si="42">AX17*(1+$BA$23)</f>
-        <v>35001.031865043122</v>
+        <v>33540.111364634904</v>
       </c>
       <c r="AZ17" s="1">
         <f t="shared" si="42"/>
-        <v>34651.021546392687</v>
+        <v>33204.710250988552</v>
       </c>
       <c r="BA17" s="1">
         <f t="shared" si="42"/>
-        <v>34304.511330928763</v>
+        <v>32872.663148478663</v>
       </c>
       <c r="BB17" s="1">
         <f t="shared" si="42"/>
-        <v>33961.466217619476</v>
+        <v>32543.936516993876</v>
       </c>
       <c r="BC17" s="1">
         <f t="shared" si="42"/>
-        <v>33621.851555443282</v>
+        <v>32218.497151823936</v>
       </c>
       <c r="BD17" s="1">
         <f t="shared" si="42"/>
-        <v>33285.633039888846</v>
+        <v>31896.312180305697</v>
       </c>
       <c r="BE17" s="1">
         <f t="shared" si="42"/>
-        <v>32952.776709489954</v>
+        <v>31577.349058502637</v>
       </c>
       <c r="BF17" s="1">
         <f t="shared" si="42"/>
-        <v>32623.248942395054</v>
+        <v>31261.575567917611</v>
       </c>
       <c r="BG17" s="1">
         <f t="shared" si="42"/>
-        <v>32297.016452971104</v>
+        <v>30948.959812238434</v>
       </c>
       <c r="BH17" s="1">
         <f t="shared" si="42"/>
-        <v>31974.046288441394</v>
+        <v>30639.470214116049</v>
       </c>
       <c r="BI17" s="1">
         <f t="shared" si="42"/>
-        <v>31654.305825556981</v>
+        <v>30333.075511974886</v>
       </c>
       <c r="BJ17" s="1">
         <f t="shared" si="42"/>
-        <v>31337.76276730141</v>
+        <v>30029.744756855136</v>
       </c>
       <c r="BK17" s="1">
         <f t="shared" si="42"/>
-        <v>31024.385139628397</v>
+        <v>29729.447309286585</v>
       </c>
       <c r="BL17" s="1">
         <f t="shared" si="42"/>
-        <v>30714.141288232113</v>
+        <v>29432.15283619372</v>
       </c>
       <c r="BM17" s="1">
         <f t="shared" si="42"/>
-        <v>30406.999875349793</v>
+        <v>29137.831307831781</v>
       </c>
       <c r="BN17" s="1">
         <f t="shared" si="42"/>
-        <v>30102.929876596296</v>
+        <v>28846.452994753461</v>
       </c>
       <c r="BO17" s="1">
         <f t="shared" si="42"/>
-        <v>29801.900577830333</v>
+        <v>28557.988464805927</v>
       </c>
       <c r="BP17" s="1">
         <f t="shared" si="42"/>
-        <v>29503.881572052029</v>
+        <v>28272.408580157866</v>
       </c>
       <c r="BQ17" s="1">
         <f t="shared" si="42"/>
-        <v>29208.842756331509</v>
+        <v>27989.684494356286</v>
       </c>
       <c r="BR17" s="1">
         <f t="shared" si="42"/>
-        <v>28916.754328768195</v>
+        <v>27709.787649412723</v>
       </c>
       <c r="BS17" s="1">
         <f t="shared" si="42"/>
-        <v>28627.586785480511</v>
+        <v>27432.689772918595</v>
       </c>
       <c r="BT17" s="1">
         <f t="shared" si="42"/>
-        <v>28341.310917625706</v>
+        <v>27158.36287518941</v>
       </c>
       <c r="BU17" s="1">
         <f t="shared" si="42"/>
-        <v>28057.897808449448</v>
+        <v>26886.779246437516</v>
       </c>
       <c r="BV17" s="1">
         <f t="shared" si="42"/>
-        <v>27777.318830364955</v>
+        <v>26617.911453973142</v>
       </c>
       <c r="BW17" s="1">
         <f t="shared" si="42"/>
-        <v>27499.545642061305</v>
+        <v>26351.732339433409</v>
       </c>
       <c r="BX17" s="1">
         <f t="shared" si="42"/>
-        <v>27224.550185640692</v>
+        <v>26088.215016039074</v>
       </c>
       <c r="BY17" s="1">
         <f t="shared" si="42"/>
-        <v>26952.304683784285</v>
+        <v>25827.332865878681</v>
       </c>
       <c r="BZ17" s="1">
         <f t="shared" si="42"/>
-        <v>26682.781636946442</v>
+        <v>25569.059537219895</v>
       </c>
       <c r="CA17" s="1">
         <f t="shared" si="42"/>
-        <v>26415.953820576979</v>
+        <v>25313.368941847697</v>
       </c>
       <c r="CB17" s="1">
         <f t="shared" si="42"/>
-        <v>26151.794282371207</v>
+        <v>25060.235252429218</v>
       </c>
       <c r="CC17" s="1">
         <f t="shared" si="42"/>
-        <v>25890.276339547494</v>
+        <v>24809.632899904926</v>
       </c>
       <c r="CD17" s="1">
         <f t="shared" si="42"/>
-        <v>25631.373576152018</v>
+        <v>24561.536570905875</v>
       </c>
       <c r="CE17" s="1">
         <f t="shared" ref="CE17:DJ17" si="43">CD17*(1+$BA$23)</f>
-        <v>25375.059840390499</v>
+        <v>24315.921205196817</v>
       </c>
       <c r="CF17" s="1">
         <f t="shared" si="43"/>
-        <v>25121.309241986593</v>
+        <v>24072.76199314485</v>
       </c>
       <c r="CG17" s="1">
         <f t="shared" si="43"/>
-        <v>24870.096149566729</v>
+        <v>23832.034373213402</v>
       </c>
       <c r="CH17" s="1">
         <f t="shared" si="43"/>
-        <v>24621.395188071063</v>
+        <v>23593.714029481267</v>
       </c>
       <c r="CI17" s="1">
         <f t="shared" si="43"/>
-        <v>24375.18123619035</v>
+        <v>23357.776889186454</v>
       </c>
       <c r="CJ17" s="1">
         <f t="shared" si="43"/>
-        <v>24131.429423828446</v>
+        <v>23124.19912029459</v>
       </c>
       <c r="CK17" s="1">
         <f t="shared" si="43"/>
-        <v>23890.115129590162</v>
+        <v>22892.957129091643</v>
       </c>
       <c r="CL17" s="1">
         <f t="shared" si="43"/>
-        <v>23651.213978294261</v>
+        <v>22664.027557800728</v>
       </c>
       <c r="CM17" s="1">
         <f t="shared" si="43"/>
-        <v>23414.701838511319</v>
+        <v>22437.38728222272</v>
       </c>
       <c r="CN17" s="1">
         <f t="shared" si="43"/>
-        <v>23180.554820126206</v>
+        <v>22213.013409400493</v>
       </c>
       <c r="CO17" s="1">
         <f t="shared" si="43"/>
-        <v>22948.749271924946</v>
+        <v>21990.883275306489</v>
       </c>
       <c r="CP17" s="1">
         <f t="shared" si="43"/>
-        <v>22719.261779205695</v>
+        <v>21770.974442553423</v>
       </c>
       <c r="CQ17" s="1">
         <f t="shared" si="43"/>
-        <v>22492.069161413638</v>
+        <v>21553.264698127889</v>
       </c>
       <c r="CR17" s="1">
         <f t="shared" si="43"/>
-        <v>22267.1484697995</v>
+        <v>21337.73205114661</v>
       </c>
       <c r="CS17" s="1">
         <f t="shared" si="43"/>
-        <v>22044.476985101504</v>
+        <v>21124.354730635143</v>
       </c>
       <c r="CT17" s="1">
         <f t="shared" si="43"/>
-        <v>21824.032215250489</v>
+        <v>20913.111183328791</v>
       </c>
       <c r="CU17" s="1">
         <f t="shared" si="43"/>
-        <v>21605.791893097983</v>
+        <v>20703.980071495502</v>
       </c>
       <c r="CV17" s="1">
         <f t="shared" si="43"/>
-        <v>21389.733974167004</v>
+        <v>20496.940270780546</v>
       </c>
       <c r="CW17" s="1">
         <f t="shared" si="43"/>
-        <v>21175.836634425334</v>
+        <v>20291.970868072742</v>
       </c>
       <c r="CX17" s="1">
         <f t="shared" si="43"/>
-        <v>20964.078268081081</v>
+        <v>20089.051159392013</v>
       </c>
       <c r="CY17" s="1">
         <f t="shared" si="43"/>
-        <v>20754.437485400271</v>
+        <v>19888.160647798093</v>
       </c>
       <c r="CZ17" s="1">
         <f t="shared" si="43"/>
-        <v>20546.893110546269</v>
+        <v>19689.279041320111</v>
       </c>
       <c r="DA17" s="1">
         <f t="shared" si="43"/>
-        <v>20341.424179440804</v>
+        <v>19492.386250906911</v>
       </c>
       <c r="DB17" s="1">
         <f t="shared" si="43"/>
-        <v>20138.009937646395</v>
+        <v>19297.462388397842</v>
       </c>
       <c r="DC17" s="1">
         <f t="shared" si="43"/>
-        <v>19936.629838269931</v>
+        <v>19104.487764513862</v>
       </c>
       <c r="DD17" s="1">
         <f t="shared" si="43"/>
-        <v>19737.263539887233</v>
+        <v>18913.442886868725</v>
       </c>
       <c r="DE17" s="1">
         <f t="shared" si="43"/>
-        <v>19539.890904488362</v>
+        <v>18724.308458000036</v>
       </c>
       <c r="DF17" s="1">
         <f t="shared" si="43"/>
-        <v>19344.491995443477</v>
+        <v>18537.065373420035</v>
       </c>
       <c r="DG17" s="1">
         <f t="shared" si="43"/>
-        <v>19151.047075489041</v>
+        <v>18351.694719685835</v>
       </c>
       <c r="DH17" s="1">
         <f t="shared" si="43"/>
-        <v>18959.536604734152</v>
+        <v>18168.177772488976</v>
       </c>
       <c r="DI17" s="1">
         <f t="shared" si="43"/>
-        <v>18769.94123868681</v>
+        <v>17986.495994764085</v>
       </c>
       <c r="DJ17" s="1">
         <f t="shared" si="43"/>
-        <v>18582.241826299942</v>
+        <v>17806.631034816444</v>
       </c>
       <c r="DK17" s="1">
         <f t="shared" ref="DK17:EI17" si="44">DJ17*(1+$BA$23)</f>
-        <v>18396.419408036942</v>
+        <v>17628.56472446828</v>
       </c>
       <c r="DL17" s="1">
         <f t="shared" si="44"/>
-        <v>18212.455213956571</v>
+        <v>17452.279077223597</v>
       </c>
       <c r="DM17" s="1">
         <f t="shared" si="44"/>
-        <v>18030.330661817006</v>
+        <v>17277.75628645136</v>
       </c>
       <c r="DN17" s="1">
         <f t="shared" si="44"/>
-        <v>17850.027355198836</v>
+        <v>17104.978723586846</v>
       </c>
       <c r="DO17" s="1">
         <f t="shared" si="44"/>
-        <v>17671.527081646847</v>
+        <v>16933.928936350978</v>
       </c>
       <c r="DP17" s="1">
         <f t="shared" si="44"/>
-        <v>17494.811810830379</v>
+        <v>16764.589646987468</v>
       </c>
       <c r="DQ17" s="1">
         <f t="shared" si="44"/>
-        <v>17319.863692722076</v>
+        <v>16596.943750517592</v>
       </c>
       <c r="DR17" s="1">
         <f t="shared" si="44"/>
-        <v>17146.665055794856</v>
+        <v>16430.974313012415</v>
       </c>
       <c r="DS17" s="1">
         <f t="shared" si="44"/>
-        <v>16975.198405236908</v>
+        <v>16266.66456988229</v>
       </c>
       <c r="DT17" s="1">
         <f t="shared" si="44"/>
-        <v>16805.446421184537</v>
+        <v>16103.997924183468</v>
       </c>
       <c r="DU17" s="1">
         <f t="shared" si="44"/>
-        <v>16637.391956972693</v>
+        <v>15942.957944941632</v>
       </c>
       <c r="DV17" s="1">
         <f t="shared" si="44"/>
-        <v>16471.018037402966</v>
+        <v>15783.528365492215</v>
       </c>
       <c r="DW17" s="1">
         <f t="shared" si="44"/>
-        <v>16306.307857028936</v>
+        <v>15625.693081837293</v>
       </c>
       <c r="DX17" s="1">
         <f t="shared" si="44"/>
-        <v>16143.244778458647</v>
+        <v>15469.436151018919</v>
       </c>
       <c r="DY17" s="1">
         <f t="shared" si="44"/>
-        <v>15981.812330674062</v>
+        <v>15314.741789508729</v>
       </c>
       <c r="DZ17" s="1">
         <f t="shared" si="44"/>
-        <v>15821.994207367321</v>
+        <v>15161.594371613643</v>
       </c>
       <c r="EA17" s="1">
         <f t="shared" si="44"/>
-        <v>15663.774265293647</v>
+        <v>15009.978427897506</v>
       </c>
       <c r="EB17" s="1">
         <f t="shared" si="44"/>
-        <v>15507.136522640711</v>
+        <v>14859.878643618531</v>
       </c>
       <c r="EC17" s="1">
         <f t="shared" si="44"/>
-        <v>15352.065157414303</v>
+        <v>14711.279857182346</v>
       </c>
       <c r="ED17" s="1">
         <f t="shared" si="44"/>
-        <v>15198.54450584016</v>
+        <v>14564.167058610523</v>
       </c>
       <c r="EE17" s="1">
         <f t="shared" si="44"/>
-        <v>15046.559060781758</v>
+        <v>14418.525388024418</v>
       </c>
       <c r="EF17" s="1">
         <f t="shared" si="44"/>
-        <v>14896.093470173941</v>
+        <v>14274.340134144173</v>
       </c>
       <c r="EG17" s="1">
         <f t="shared" si="44"/>
-        <v>14747.132535472201</v>
+        <v>14131.596732802731</v>
       </c>
       <c r="EH17" s="1">
         <f t="shared" si="44"/>
-        <v>14599.66121011748</v>
+        <v>13990.280765474703</v>
       </c>
       <c r="EI17" s="1">
         <f t="shared" si="44"/>
-        <v>14453.664598016305</v>
+        <v>13850.377957819956</v>
       </c>
     </row>
     <row r="18" spans="2:139" x14ac:dyDescent="0.3">
@@ -3762,11 +3853,11 @@
       </c>
       <c r="C18" s="5">
         <f>C47/Main!$D$13</f>
-        <v>19.870541433483918</v>
+        <v>19.041157847127995</v>
       </c>
       <c r="D18" s="5">
         <f>D47/Main!$D$13</f>
-        <v>19.870541433483918</v>
+        <v>19.041157847127995</v>
       </c>
       <c r="E18" s="5">
         <f t="shared" ref="E18:H18" si="45">E47/2</f>
@@ -3803,18 +3894,24 @@
       <c r="T18" s="5"/>
       <c r="U18" s="5"/>
       <c r="V18" s="5"/>
-      <c r="W18" s="13">
-        <f t="shared" ref="W18" si="47">W47/2</f>
-        <v>1415.5</v>
-      </c>
-      <c r="X18" s="5"/>
+      <c r="W18" s="5">
+        <f t="shared" ref="W18:X18" si="47">(15795-2762)/10</f>
+        <v>1303.3</v>
+      </c>
+      <c r="X18" s="5">
+        <f t="shared" si="47"/>
+        <v>1303.3</v>
+      </c>
       <c r="Y18" s="5"/>
       <c r="Z18" s="5"/>
-      <c r="AA18" s="13">
-        <f t="shared" ref="AA18" si="48">AA47/2</f>
-        <v>1415.5</v>
-      </c>
-      <c r="AB18" s="5"/>
+      <c r="AA18" s="5">
+        <f t="shared" ref="AA18:AB18" si="48">(15795-2762)/10</f>
+        <v>1303.3</v>
+      </c>
+      <c r="AB18" s="5">
+        <f t="shared" si="48"/>
+        <v>1303.3</v>
+      </c>
       <c r="AC18" s="5"/>
       <c r="AD18" s="5"/>
       <c r="AF18" s="13">
@@ -3854,44 +3951,44 @@
         <v>1415.5</v>
       </c>
       <c r="AO18" s="5">
-        <f t="shared" ref="AO18:AX18" si="51">13048.9/10</f>
-        <v>1304.8899999999999</v>
+        <f>(15795-2762)/10</f>
+        <v>1303.3</v>
       </c>
       <c r="AP18" s="5">
-        <f t="shared" si="51"/>
-        <v>1304.8899999999999</v>
+        <f>(15795-2762)/10</f>
+        <v>1303.3</v>
       </c>
       <c r="AQ18" s="5">
-        <f t="shared" si="51"/>
-        <v>1304.8899999999999</v>
+        <f>(15795-2762)/10</f>
+        <v>1303.3</v>
       </c>
       <c r="AR18" s="5">
-        <f t="shared" si="51"/>
-        <v>1304.8899999999999</v>
+        <f>(15795-2762)/10</f>
+        <v>1303.3</v>
       </c>
       <c r="AS18" s="5">
-        <f t="shared" si="51"/>
-        <v>1304.8899999999999</v>
+        <f>(15795-2762)/10</f>
+        <v>1303.3</v>
       </c>
       <c r="AT18" s="5">
-        <f t="shared" si="51"/>
-        <v>1304.8899999999999</v>
+        <f>(15795-2762)/10</f>
+        <v>1303.3</v>
       </c>
       <c r="AU18" s="5">
-        <f t="shared" si="51"/>
-        <v>1304.8899999999999</v>
+        <f>(15795-2762)/10</f>
+        <v>1303.3</v>
       </c>
       <c r="AV18" s="5">
-        <f t="shared" si="51"/>
-        <v>1304.8899999999999</v>
+        <f>(15795-2762)/10</f>
+        <v>1303.3</v>
       </c>
       <c r="AW18" s="5">
-        <f t="shared" si="51"/>
-        <v>1304.8899999999999</v>
+        <f>(15795-2762)/10</f>
+        <v>1303.3</v>
       </c>
       <c r="AX18" s="5">
-        <f t="shared" si="51"/>
-        <v>1304.8899999999999</v>
+        <f>(15795-2762)/10</f>
+        <v>1303.3</v>
       </c>
     </row>
     <row r="19" spans="2:139" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3900,35 +3997,35 @@
       </c>
       <c r="C19" s="18">
         <f>C48/Main!$D$13</f>
-        <v>1.4165456542765034</v>
+        <v>1.3574199520950327</v>
       </c>
       <c r="D19" s="18">
         <f>D48/Main!$D$13</f>
-        <v>1.2135596628243874</v>
+        <v>1.1629064650351157</v>
       </c>
       <c r="E19" s="18">
         <f>E48/Main!$D$13</f>
-        <v>1.2796589796905786</v>
+        <v>1.2262468390379899</v>
       </c>
       <c r="F19" s="18">
         <f>F48/Main!$D$13</f>
-        <v>0.74885561124742683</v>
+        <v>0.7175988609168823</v>
       </c>
       <c r="G19" s="18">
         <f>G48/Main!$D$13</f>
-        <v>0.36342955653490128</v>
+        <v>0.34826024119461918</v>
       </c>
       <c r="H19" s="18">
         <f>H48/Main!$D$13</f>
-        <v>1.0765448621829243</v>
+        <v>1.0316105738214738</v>
       </c>
       <c r="I19" s="18">
         <f>I48/Main!$D$13</f>
-        <v>1.7330717585460196</v>
+        <v>1.6607344608771737</v>
       </c>
       <c r="J19" s="18">
         <f>J17/J18</f>
-        <v>2.1001355826296537</v>
+        <v>2.0136875143318287</v>
       </c>
       <c r="K19" s="18"/>
       <c r="L19" s="18"/>
@@ -3943,94 +4040,100 @@
       <c r="U19" s="18"/>
       <c r="V19" s="18"/>
       <c r="W19" s="14">
-        <f t="shared" ref="W19" si="52">W17/W18</f>
-        <v>6.3534472375577513</v>
-      </c>
-      <c r="X19" s="18"/>
+        <f t="shared" ref="W19:X19" si="51">W17/W18</f>
+        <v>6.6123914918765179</v>
+      </c>
+      <c r="X19" s="14">
+        <f t="shared" si="51"/>
+        <v>2.8422539865936707</v>
+      </c>
       <c r="Y19" s="18"/>
       <c r="Z19" s="18"/>
       <c r="AA19" s="14">
-        <f t="shared" ref="AA19" si="53">AA17/AA18</f>
-        <v>4.0076871263640763</v>
-      </c>
-      <c r="AB19" s="18"/>
+        <f t="shared" ref="AA19:AB19" si="52">AA17/AA18</f>
+        <v>4.1710264153636949</v>
+      </c>
+      <c r="AB19" s="14">
+        <f t="shared" si="52"/>
+        <v>4.6208514952037421</v>
+      </c>
       <c r="AC19" s="18"/>
       <c r="AD19" s="18"/>
       <c r="AF19" s="14">
         <f>AF48/Main!$D$13</f>
-        <v>4.1895138112680774</v>
+        <v>4.0146462063007595</v>
       </c>
       <c r="AG19" s="14">
         <f>AG17/AG18</f>
-        <v>11.412293013215265</v>
+        <v>10.935951261807558</v>
       </c>
       <c r="AH19" s="14">
-        <f t="shared" ref="AH19:AS19" si="54">AH17/AH18</f>
-        <v>8.8439727560023123</v>
+        <f t="shared" ref="AH19:AS19" si="53">AH17/AH18</f>
+        <v>8.4748310360063499</v>
       </c>
       <c r="AI19" s="14">
+        <f t="shared" si="53"/>
+        <v>9.2941824295652111</v>
+      </c>
+      <c r="AJ19" s="14">
+        <f t="shared" ref="AJ19:AN19" si="54">AJ17/AJ18</f>
+        <v>10.248732939412356</v>
+      </c>
+      <c r="AK19" s="14">
         <f t="shared" si="54"/>
-        <v>9.6990129770332931</v>
-      </c>
-      <c r="AJ19" s="14">
-        <f t="shared" ref="AJ19:AN19" si="55">AJ17/AJ18</f>
-        <v>10.695141238169041</v>
-      </c>
-      <c r="AK19" s="14">
+        <v>13.009626047580042</v>
+      </c>
+      <c r="AL19" s="14">
+        <f t="shared" si="54"/>
+        <v>11.198431272557286</v>
+      </c>
+      <c r="AM19" s="14">
+        <f t="shared" si="54"/>
+        <v>22.571668715376173</v>
+      </c>
+      <c r="AN19" s="14">
+        <f t="shared" si="54"/>
+        <v>21.750733366796464</v>
+      </c>
+      <c r="AO19" s="14">
+        <f t="shared" si="53"/>
+        <v>19.195957723293859</v>
+      </c>
+      <c r="AP19" s="14">
+        <f t="shared" si="53"/>
+        <v>19.760070229499235</v>
+      </c>
+      <c r="AQ19" s="14">
+        <f t="shared" si="53"/>
+        <v>21.907581054453846</v>
+      </c>
+      <c r="AR19" s="14">
+        <f t="shared" si="53"/>
+        <v>24.096684032058128</v>
+      </c>
+      <c r="AS19" s="14">
+        <f t="shared" si="53"/>
+        <v>24.401941680151225</v>
+      </c>
+      <c r="AT19" s="14">
+        <f t="shared" ref="AT19:AX19" si="55">AT17/AT18</f>
+        <v>24.711537720880706</v>
+      </c>
+      <c r="AU19" s="14">
         <f t="shared" si="55"/>
-        <v>13.576291709149505</v>
-      </c>
-      <c r="AL19" s="14">
+        <v>25.025541254496037</v>
+      </c>
+      <c r="AV19" s="14">
         <f t="shared" si="55"/>
-        <v>11.686205974335454</v>
-      </c>
-      <c r="AM19" s="14">
+        <v>25.344022586575651</v>
+      </c>
+      <c r="AW19" s="14">
         <f t="shared" si="55"/>
-        <v>23.554832223577442</v>
-      </c>
-      <c r="AN19" s="14">
+        <v>25.667053250366756</v>
+      </c>
+      <c r="AX19" s="14">
         <f t="shared" si="55"/>
-        <v>22.698139054541763</v>
-      </c>
-      <c r="AO19" s="14">
-        <f t="shared" si="54"/>
-        <v>23.828207698223537</v>
-      </c>
-      <c r="AP19" s="14">
-        <f t="shared" si="54"/>
-        <v>24.492584832174977</v>
-      </c>
-      <c r="AQ19" s="14">
-        <f t="shared" si="54"/>
-        <v>24.801918022809918</v>
-      </c>
-      <c r="AR19" s="14">
-        <f t="shared" si="54"/>
-        <v>25.115632692197472</v>
-      </c>
-      <c r="AS19" s="14">
-        <f t="shared" si="54"/>
-        <v>25.433798418062096</v>
-      </c>
-      <c r="AT19" s="14">
-        <f t="shared" ref="AT19:AX19" si="56">AT17/AT18</f>
-        <v>25.756485989164229</v>
-      </c>
-      <c r="AU19" s="14">
-        <f t="shared" si="56"/>
-        <v>26.083767427715802</v>
-      </c>
-      <c r="AV19" s="14">
-        <f t="shared" si="56"/>
-        <v>26.415716012226088</v>
-      </c>
-      <c r="AW19" s="14">
-        <f t="shared" si="56"/>
-        <v>26.752406300786152</v>
-      </c>
-      <c r="AX19" s="14">
-        <f t="shared" si="56"/>
-        <v>27.093914154800558</v>
+        <v>25.994706029554276</v>
       </c>
     </row>
     <row r="21" spans="2:139" x14ac:dyDescent="0.3">
@@ -4046,15 +4149,15 @@
         <v>-0.40414022402782546</v>
       </c>
       <c r="H21" s="11">
-        <f t="shared" ref="H21:J21" si="57">H3/D3-1</f>
+        <f t="shared" ref="H21:J21" si="56">H3/D3-1</f>
         <v>-0.11294704048865234</v>
       </c>
       <c r="I21" s="11">
-        <f t="shared" si="57"/>
-        <v>7.111393177307046E-2</v>
+        <f t="shared" si="56"/>
+        <v>7.1113931773070238E-2</v>
       </c>
       <c r="J21" s="11">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="K21" s="11"/>
@@ -4074,84 +4177,87 @@
       <c r="Y21" s="11"/>
       <c r="Z21" s="11"/>
       <c r="AA21" s="11">
-        <f t="shared" ref="AA21" si="58">AA3/W3-1</f>
-        <v>3.5094715869286919E-2</v>
-      </c>
-      <c r="AB21" s="11"/>
+        <f t="shared" ref="AA21:AB21" si="57">AA3/W3-1</f>
+        <v>3.5094715869287141E-2</v>
+      </c>
+      <c r="AB21" s="11">
+        <f t="shared" si="57"/>
+        <v>8.1510787953519737E-2</v>
+      </c>
       <c r="AC21" s="11"/>
       <c r="AD21" s="11"/>
       <c r="AE21" s="1"/>
       <c r="AF21" s="11"/>
       <c r="AG21" s="11">
-        <f t="shared" ref="AG21:AS21" si="59">AG3/AF3-1</f>
+        <f t="shared" ref="AG21:AS21" si="58">AG3/AF3-1</f>
         <v>6.4583271204430082E-2</v>
       </c>
       <c r="AH21" s="11">
-        <f t="shared" si="59"/>
-        <v>2.8801399342603062E-2</v>
+        <f t="shared" si="58"/>
+        <v>2.880139934260284E-2</v>
       </c>
       <c r="AI21" s="11">
-        <f t="shared" si="59"/>
-        <v>-1.1881750488930254E-2</v>
+        <f t="shared" si="58"/>
+        <v>-1.1881750488930143E-2</v>
       </c>
       <c r="AJ21" s="11">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>-8.8793424964727308E-2</v>
       </c>
       <c r="AK21" s="11">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>0.15303968892572861</v>
       </c>
       <c r="AL21" s="11">
-        <f t="shared" si="59"/>
-        <v>0.18403064777276468</v>
+        <f t="shared" si="58"/>
+        <v>0.18403064777276446</v>
       </c>
       <c r="AM21" s="11">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>0.21373104667460008</v>
       </c>
       <c r="AN21" s="11">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>6.5225807774974331E-2</v>
       </c>
       <c r="AO21" s="11">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AP21" s="11">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AQ21" s="11">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR21" s="11">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AS21" s="11">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AT21" s="11">
-        <f t="shared" ref="AT21" si="60">AT3/AS3-1</f>
+        <f t="shared" ref="AT21" si="59">AT3/AS3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AU21" s="11">
-        <f t="shared" ref="AU21" si="61">AU3/AT3-1</f>
+        <f t="shared" ref="AU21" si="60">AU3/AT3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AV21" s="11">
-        <f t="shared" ref="AV21" si="62">AV3/AU3-1</f>
+        <f t="shared" ref="AV21" si="61">AV3/AU3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW21" s="11">
-        <f t="shared" ref="AW21" si="63">AW3/AV3-1</f>
+        <f t="shared" ref="AW21" si="62">AW3/AV3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX21" s="11">
-        <f t="shared" ref="AX21" si="64">AX3/AW3-1</f>
+        <f t="shared" ref="AX21" si="63">AX3/AW3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -4160,36 +4266,36 @@
         <v>40</v>
       </c>
       <c r="C22" s="11">
-        <f t="shared" ref="C22:J22" si="65">C5/C3</f>
-        <v>0.18806847005668625</v>
+        <f t="shared" ref="C22:J22" si="64">C5/C3</f>
+        <v>0.18806847005668623</v>
       </c>
       <c r="D22" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>0.17697934949359723</v>
       </c>
       <c r="E22" s="11">
-        <f t="shared" si="65"/>
-        <v>0.18165166696872398</v>
+        <f t="shared" si="64"/>
+        <v>0.18165166696872401</v>
       </c>
       <c r="F22" s="11">
-        <f t="shared" si="65"/>
-        <v>0.17324862570167951</v>
+        <f t="shared" si="64"/>
+        <v>0.17324862570167954</v>
       </c>
       <c r="G22" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>0.11942020467762535</v>
       </c>
       <c r="H22" s="11">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>0.16948252597599769</v>
       </c>
       <c r="I22" s="11">
-        <f t="shared" si="65"/>
-        <v>0.20327552088139039</v>
+        <f t="shared" si="64"/>
+        <v>0.20327552088139042</v>
       </c>
       <c r="J22" s="11">
-        <f t="shared" si="65"/>
-        <v>0.18000000000000002</v>
+        <f t="shared" si="64"/>
+        <v>0.18</v>
       </c>
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
@@ -4204,94 +4310,100 @@
       <c r="U22" s="11"/>
       <c r="V22" s="11"/>
       <c r="W22" s="11">
-        <f t="shared" ref="W22" si="66">W5/W3</f>
-        <v>0.20517991440865377</v>
-      </c>
-      <c r="X22" s="11"/>
+        <f t="shared" ref="W22:X22" si="65">W5/W3</f>
+        <v>0.2051799144086538</v>
+      </c>
+      <c r="X22" s="11">
+        <f t="shared" si="65"/>
+        <v>0.21303035299444603</v>
+      </c>
       <c r="Y22" s="11"/>
       <c r="Z22" s="11"/>
       <c r="AA22" s="11">
-        <f t="shared" ref="AA22" si="67">AA5/AA3</f>
+        <f t="shared" ref="AA22:AB22" si="66">AA5/AA3</f>
         <v>0.17920138581149314</v>
       </c>
-      <c r="AB22" s="11"/>
+      <c r="AB22" s="11">
+        <f t="shared" si="66"/>
+        <v>0.15906682382372364</v>
+      </c>
       <c r="AC22" s="11"/>
       <c r="AD22" s="11"/>
       <c r="AE22" s="1"/>
       <c r="AF22" s="11">
-        <f t="shared" ref="AF22:AS22" si="68">AF5/AF3</f>
+        <f t="shared" ref="AF22:AS22" si="67">AF5/AF3</f>
         <v>0.17620839191869986</v>
       </c>
       <c r="AG22" s="11">
-        <f t="shared" si="68"/>
-        <v>0.18687707861703617</v>
+        <f t="shared" si="67"/>
+        <v>0.18687707861703615</v>
       </c>
       <c r="AH22" s="11">
-        <f t="shared" si="68"/>
-        <v>0.18010829929687935</v>
+        <f t="shared" si="67"/>
+        <v>0.18010829929687938</v>
       </c>
       <c r="AI22" s="11">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0.18017469511959316</v>
       </c>
       <c r="AJ22" s="11">
-        <f t="shared" si="68"/>
-        <v>0.1775655370791128</v>
+        <f t="shared" si="67"/>
+        <v>0.17756553707911277</v>
       </c>
       <c r="AK22" s="11">
-        <f t="shared" si="68"/>
-        <v>0.19030486999046864</v>
+        <f t="shared" si="67"/>
+        <v>0.19030486999046861</v>
       </c>
       <c r="AL22" s="11">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0.16991347811227653</v>
       </c>
       <c r="AM22" s="11">
-        <f t="shared" si="68"/>
-        <v>0.20774477176957923</v>
+        <f t="shared" si="67"/>
+        <v>0.2077447717695792</v>
       </c>
       <c r="AN22" s="11">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>0.19938999145320213</v>
       </c>
       <c r="AO22" s="11">
+        <f t="shared" si="67"/>
+        <v>0.17</v>
+      </c>
+      <c r="AP22" s="11">
+        <f t="shared" si="67"/>
+        <v>0.17</v>
+      </c>
+      <c r="AQ22" s="11">
+        <f t="shared" si="67"/>
+        <v>0.18</v>
+      </c>
+      <c r="AR22" s="11">
+        <f t="shared" si="67"/>
+        <v>0.19</v>
+      </c>
+      <c r="AS22" s="11">
+        <f t="shared" si="67"/>
+        <v>0.19</v>
+      </c>
+      <c r="AT22" s="11">
+        <f t="shared" ref="AT22:AX22" si="68">AT5/AT3</f>
+        <v>0.19</v>
+      </c>
+      <c r="AU22" s="11">
         <f t="shared" si="68"/>
         <v>0.19</v>
       </c>
-      <c r="AP22" s="11">
+      <c r="AV22" s="11">
         <f t="shared" si="68"/>
         <v>0.19</v>
       </c>
-      <c r="AQ22" s="11">
+      <c r="AW22" s="11">
         <f t="shared" si="68"/>
         <v>0.19</v>
       </c>
-      <c r="AR22" s="11">
+      <c r="AX22" s="11">
         <f t="shared" si="68"/>
-        <v>0.19</v>
-      </c>
-      <c r="AS22" s="11">
-        <f t="shared" si="68"/>
-        <v>0.18999999999999997</v>
-      </c>
-      <c r="AT22" s="11">
-        <f t="shared" ref="AT22:AX22" si="69">AT5/AT3</f>
-        <v>0.19</v>
-      </c>
-      <c r="AU22" s="11">
-        <f t="shared" si="69"/>
-        <v>0.19000000000000003</v>
-      </c>
-      <c r="AV22" s="11">
-        <f t="shared" si="69"/>
-        <v>0.19</v>
-      </c>
-      <c r="AW22" s="11">
-        <f t="shared" si="69"/>
-        <v>0.19</v>
-      </c>
-      <c r="AX22" s="11">
-        <f t="shared" si="69"/>
         <v>0.19</v>
       </c>
     </row>
@@ -4300,36 +4412,36 @@
         <v>41</v>
       </c>
       <c r="C23" s="15">
-        <f t="shared" ref="C23:J23" si="70">C7/C3</f>
+        <f t="shared" ref="C23:J23" si="69">C7/C3</f>
         <v>9.5918250785848397E-2</v>
       </c>
       <c r="D23" s="15">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>8.6238923012217888E-2</v>
       </c>
       <c r="E23" s="15">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>8.4124432196848675E-2</v>
       </c>
       <c r="F23" s="15">
-        <f t="shared" si="70"/>
-        <v>5.2166736552588591E-2</v>
+        <f t="shared" si="69"/>
+        <v>5.2166736552588584E-2</v>
       </c>
       <c r="G23" s="15">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>3.0255634025068705E-3</v>
       </c>
       <c r="H23" s="15">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>7.4701668495357615E-2</v>
       </c>
       <c r="I23" s="15">
-        <f t="shared" si="70"/>
-        <v>0.12121915594932633</v>
+        <f t="shared" si="69"/>
+        <v>0.12121915594932635</v>
       </c>
       <c r="J23" s="15">
-        <f t="shared" si="70"/>
-        <v>8.3134488680727259E-2</v>
+        <f t="shared" si="69"/>
+        <v>8.3134488680727217E-2</v>
       </c>
       <c r="K23" s="15"/>
       <c r="L23" s="15"/>
@@ -4344,94 +4456,100 @@
       <c r="U23" s="15"/>
       <c r="V23" s="15"/>
       <c r="W23" s="15">
-        <f t="shared" ref="W23" si="71">W7/W3</f>
-        <v>0.11056972283632903</v>
-      </c>
-      <c r="X23" s="15"/>
+        <f t="shared" ref="W23:X23" si="70">W7/W3</f>
+        <v>0.11056972283632904</v>
+      </c>
+      <c r="X23" s="15">
+        <f t="shared" si="70"/>
+        <v>0.10094795165323366</v>
+      </c>
       <c r="Y23" s="15"/>
       <c r="Z23" s="15"/>
       <c r="AA23" s="15">
-        <f t="shared" ref="AA23" si="72">AA7/AA3</f>
-        <v>9.5169344225396441E-2</v>
-      </c>
-      <c r="AB23" s="15"/>
+        <f t="shared" ref="AA23:AB23" si="71">AA7/AA3</f>
+        <v>9.5169344225396427E-2</v>
+      </c>
+      <c r="AB23" s="15">
+        <f t="shared" si="71"/>
+        <v>6.7829202305131744E-2</v>
+      </c>
       <c r="AC23" s="15"/>
       <c r="AD23" s="15"/>
       <c r="AF23" s="15">
-        <f t="shared" ref="AF23:AS23" si="73">AF7/AF3</f>
+        <f t="shared" ref="AF23:AS23" si="72">AF7/AF3</f>
         <v>7.2267204856667849E-2</v>
       </c>
       <c r="AG23" s="15">
+        <f t="shared" si="72"/>
+        <v>8.1684888549877099E-2</v>
+      </c>
+      <c r="AH23" s="15">
+        <f t="shared" si="72"/>
+        <v>8.1637366582410498E-2</v>
+      </c>
+      <c r="AI23" s="15">
+        <f t="shared" si="72"/>
+        <v>8.0331716954089125E-2</v>
+      </c>
+      <c r="AJ23" s="15">
+        <f t="shared" si="72"/>
+        <v>8.0756266288595002E-2</v>
+      </c>
+      <c r="AK23" s="15">
+        <f t="shared" si="72"/>
+        <v>9.5466636872274621E-2</v>
+      </c>
+      <c r="AL23" s="15">
+        <f t="shared" si="72"/>
+        <v>7.3343493126959355E-2</v>
+      </c>
+      <c r="AM23" s="15">
+        <f t="shared" si="72"/>
+        <v>0.11870265931113701</v>
+      </c>
+      <c r="AN23" s="15">
+        <f t="shared" si="72"/>
+        <v>9.983170369057795E-2</v>
+      </c>
+      <c r="AO23" s="15">
+        <f t="shared" si="72"/>
+        <v>7.2356294694349357E-2</v>
+      </c>
+      <c r="AP23" s="15">
+        <f t="shared" si="72"/>
+        <v>7.3313585922836141E-2</v>
+      </c>
+      <c r="AQ23" s="15">
+        <f t="shared" si="72"/>
+        <v>8.3313585922836109E-2</v>
+      </c>
+      <c r="AR23" s="15">
+        <f t="shared" si="72"/>
+        <v>9.3313585922836131E-2</v>
+      </c>
+      <c r="AS23" s="15">
+        <f t="shared" si="72"/>
+        <v>9.3313585922836131E-2</v>
+      </c>
+      <c r="AT23" s="15">
+        <f t="shared" ref="AT23:AX23" si="73">AT7/AT3</f>
+        <v>9.3313585922836145E-2</v>
+      </c>
+      <c r="AU23" s="15">
         <f t="shared" si="73"/>
-        <v>8.1684888549877099E-2</v>
-      </c>
-      <c r="AH23" s="15">
+        <v>9.3313585922836145E-2</v>
+      </c>
+      <c r="AV23" s="15">
         <f t="shared" si="73"/>
-        <v>8.1637366582410512E-2</v>
-      </c>
-      <c r="AI23" s="15">
+        <v>9.3313585922836159E-2</v>
+      </c>
+      <c r="AW23" s="15">
         <f t="shared" si="73"/>
-        <v>8.0331716954089138E-2</v>
-      </c>
-      <c r="AJ23" s="15">
+        <v>9.3313585922836159E-2</v>
+      </c>
+      <c r="AX23" s="15">
         <f t="shared" si="73"/>
-        <v>8.0756266288595016E-2</v>
-      </c>
-      <c r="AK23" s="15">
-        <f t="shared" si="73"/>
-        <v>9.5466636872274635E-2</v>
-      </c>
-      <c r="AL23" s="15">
-        <f t="shared" si="73"/>
-        <v>7.3343493126959355E-2</v>
-      </c>
-      <c r="AM23" s="15">
-        <f t="shared" si="73"/>
-        <v>0.11870265931113701</v>
-      </c>
-      <c r="AN23" s="15">
-        <f t="shared" si="73"/>
-        <v>9.9831703690577936E-2</v>
-      </c>
-      <c r="AO23" s="15">
-        <f t="shared" si="73"/>
-        <v>9.2356294694349347E-2</v>
-      </c>
-      <c r="AP23" s="15">
-        <f t="shared" si="73"/>
-        <v>9.3313585922836131E-2</v>
-      </c>
-      <c r="AQ23" s="15">
-        <f t="shared" si="73"/>
-        <v>9.3313585922836131E-2</v>
-      </c>
-      <c r="AR23" s="15">
-        <f t="shared" si="73"/>
-        <v>9.3313585922836118E-2</v>
-      </c>
-      <c r="AS23" s="15">
-        <f t="shared" si="73"/>
-        <v>9.3313585922836118E-2</v>
-      </c>
-      <c r="AT23" s="15">
-        <f t="shared" ref="AT23:AX23" si="74">AT7/AT3</f>
-        <v>9.3313585922836131E-2</v>
-      </c>
-      <c r="AU23" s="15">
-        <f t="shared" si="74"/>
-        <v>9.3313585922836173E-2</v>
-      </c>
-      <c r="AV23" s="15">
-        <f t="shared" si="74"/>
-        <v>9.3313585922836145E-2</v>
-      </c>
-      <c r="AW23" s="15">
-        <f t="shared" si="74"/>
-        <v>9.3313585922836187E-2</v>
-      </c>
-      <c r="AX23" s="15">
-        <f t="shared" si="74"/>
-        <v>9.3313585922836173E-2</v>
+        <v>9.3313585922836159E-2</v>
       </c>
       <c r="AZ23" t="s">
         <v>43</v>
@@ -4449,20 +4567,20 @@
       <c r="E24" s="15"/>
       <c r="F24" s="15"/>
       <c r="G24" s="15">
-        <f t="shared" ref="G24:J24" si="75">G6/C6-1</f>
+        <f t="shared" ref="G24:J24" si="74">G6/C6-1</f>
         <v>-0.24737146125812881</v>
       </c>
       <c r="H24" s="15">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>-7.3448920250799077E-2</v>
       </c>
       <c r="I24" s="15">
-        <f t="shared" si="75"/>
-        <v>-9.8798239538161692E-2</v>
+        <f t="shared" si="74"/>
+        <v>-9.8798239538161803E-2</v>
       </c>
       <c r="J24" s="15">
-        <f t="shared" si="75"/>
-        <v>-8.0000000000000071E-2</v>
+        <f t="shared" si="74"/>
+        <v>-7.999999999999996E-2</v>
       </c>
       <c r="K24" s="15"/>
       <c r="L24" s="15"/>
@@ -4481,83 +4599,86 @@
       <c r="Y24" s="15"/>
       <c r="Z24" s="15"/>
       <c r="AA24" s="15">
-        <f t="shared" ref="AA24" si="76">AA6/W6-1</f>
-        <v>-8.0636866240946348E-2</v>
-      </c>
-      <c r="AB24" s="15"/>
+        <f t="shared" ref="AA24:AB24" si="75">AA6/W6-1</f>
+        <v>-8.0636866240946237E-2</v>
+      </c>
+      <c r="AB24" s="15">
+        <f t="shared" si="75"/>
+        <v>-0.11962564364424455</v>
+      </c>
       <c r="AC24" s="15"/>
       <c r="AD24" s="15"/>
       <c r="AF24" s="15"/>
       <c r="AG24" s="15">
-        <f t="shared" ref="AG24:AS24" si="77">AG6/AF6-1</f>
+        <f t="shared" ref="AG24:AS24" si="76">AG6/AF6-1</f>
         <v>7.7396256211902825E-2</v>
       </c>
       <c r="AH24" s="15">
-        <f t="shared" si="77"/>
-        <v>-3.6933889231336559E-2</v>
+        <f t="shared" si="76"/>
+        <v>-3.6933889231336781E-2</v>
       </c>
       <c r="AI24" s="15">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>1.886202265794612E-3</v>
       </c>
       <c r="AJ24" s="15">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>-0.11648024037840821</v>
       </c>
       <c r="AK24" s="15">
-        <f t="shared" si="77"/>
-        <v>0.12956378991317563</v>
+        <f t="shared" si="76"/>
+        <v>0.12956378991317541</v>
       </c>
       <c r="AL24" s="15">
-        <f t="shared" si="77"/>
-        <v>0.20565111894345955</v>
+        <f t="shared" si="76"/>
+        <v>0.20565111894345978</v>
       </c>
       <c r="AM24" s="15">
-        <f t="shared" si="77"/>
-        <v>0.11911766755202779</v>
+        <f t="shared" si="76"/>
+        <v>0.11911766755202757</v>
       </c>
       <c r="AN24" s="15">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>0.19103258643073406</v>
       </c>
       <c r="AO24" s="15">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AP24" s="15">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AQ24" s="15">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR24" s="15">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AS24" s="15">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AT24" s="15">
-        <f t="shared" ref="AT24" si="78">AT6/AS6-1</f>
+        <f t="shared" ref="AT24" si="77">AT6/AS6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AU24" s="15">
-        <f t="shared" ref="AU24" si="79">AU6/AT6-1</f>
+        <f t="shared" ref="AU24" si="78">AU6/AT6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AV24" s="15">
-        <f t="shared" ref="AV24" si="80">AV6/AU6-1</f>
+        <f t="shared" ref="AV24" si="79">AV6/AU6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW24" s="15">
-        <f t="shared" ref="AW24" si="81">AW6/AV6-1</f>
+        <f t="shared" ref="AW24" si="80">AW6/AV6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX24" s="15">
-        <f t="shared" ref="AX24" si="82">AX6/AW6-1</f>
+        <f t="shared" ref="AX24" si="81">AX6/AW6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ24" t="s">
@@ -4572,35 +4693,35 @@
         <v>36</v>
       </c>
       <c r="C25" s="15">
-        <f t="shared" ref="C25:J25" si="83">C15/C14</f>
+        <f t="shared" ref="C25:J25" si="82">C15/C14</f>
         <v>0.25805773081515043</v>
       </c>
       <c r="D25" s="15">
-        <f t="shared" si="83"/>
+        <f t="shared" si="82"/>
         <v>0.28310079329558202</v>
       </c>
       <c r="E25" s="15">
-        <f t="shared" si="83"/>
+        <f t="shared" si="82"/>
         <v>0.2406242956077011</v>
       </c>
       <c r="F25" s="15">
-        <f t="shared" si="83"/>
-        <v>0.14590337239655096</v>
+        <f t="shared" si="82"/>
+        <v>0.14590337239655093</v>
       </c>
       <c r="G25" s="15">
-        <f t="shared" si="83"/>
+        <f t="shared" si="82"/>
         <v>-0.26400189454809952</v>
       </c>
       <c r="H25" s="15">
-        <f t="shared" si="83"/>
+        <f t="shared" si="82"/>
         <v>0.21101342653402821</v>
       </c>
       <c r="I25" s="15">
-        <f t="shared" si="83"/>
-        <v>0.23981114169367834</v>
+        <f t="shared" si="82"/>
+        <v>0.23981114169367837</v>
       </c>
       <c r="J25" s="15">
-        <f t="shared" si="83"/>
+        <f t="shared" si="82"/>
         <v>0.24</v>
       </c>
       <c r="K25" s="15"/>
@@ -4616,101 +4737,107 @@
       <c r="U25" s="15"/>
       <c r="V25" s="15"/>
       <c r="W25" s="15">
-        <f t="shared" ref="W25" si="84">W15/W14</f>
+        <f t="shared" ref="W25:X25" si="83">W15/W14</f>
         <v>0.27149721152470113</v>
       </c>
-      <c r="X25" s="15"/>
+      <c r="X25" s="15">
+        <f t="shared" si="83"/>
+        <v>0.41656882264845624</v>
+      </c>
       <c r="Y25" s="15"/>
       <c r="Z25" s="15"/>
       <c r="AA25" s="15">
-        <f t="shared" ref="AA25" si="85">AA15/AA14</f>
-        <v>0.30344478945048203</v>
-      </c>
-      <c r="AB25" s="15"/>
+        <f t="shared" ref="AA25:AB25" si="84">AA15/AA14</f>
+        <v>0.30344478945048209</v>
+      </c>
+      <c r="AB25" s="15">
+        <f t="shared" si="84"/>
+        <v>0.20639409449621729</v>
+      </c>
       <c r="AC25" s="15"/>
       <c r="AD25" s="15"/>
       <c r="AF25" s="15">
-        <f t="shared" ref="AF25:AS25" si="86">AF15/AF14</f>
+        <f t="shared" ref="AF25:AS25" si="85">AF15/AF14</f>
         <v>0.28666826205371898</v>
       </c>
       <c r="AG25" s="15">
-        <f t="shared" si="86"/>
-        <v>0.19248985566867105</v>
+        <f t="shared" si="85"/>
+        <v>0.19248985566867108</v>
       </c>
       <c r="AH25" s="15">
-        <f t="shared" si="86"/>
-        <v>0.28875699255950099</v>
+        <f t="shared" si="85"/>
+        <v>0.28875699255950105</v>
       </c>
       <c r="AI25" s="15">
-        <f t="shared" si="86"/>
-        <v>0.24412134440266059</v>
+        <f t="shared" si="85"/>
+        <v>0.24412134440266056</v>
       </c>
       <c r="AJ25" s="15">
-        <f t="shared" si="86"/>
-        <v>0.22165665480475588</v>
+        <f t="shared" si="85"/>
+        <v>0.22165665480475591</v>
       </c>
       <c r="AK25" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="85"/>
         <v>0.27964148129659938</v>
       </c>
       <c r="AL25" s="15">
-        <f t="shared" si="86"/>
-        <v>0.32030796029022002</v>
+        <f t="shared" si="85"/>
+        <v>0.32030796029021996</v>
       </c>
       <c r="AM25" s="15">
-        <f t="shared" si="86"/>
-        <v>0.2718796683744707</v>
+        <f t="shared" si="85"/>
+        <v>0.27187966837447064</v>
       </c>
       <c r="AN25" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="85"/>
         <v>0.25330305651694912</v>
       </c>
       <c r="AO25" s="15">
+        <f t="shared" si="85"/>
+        <v>0.26</v>
+      </c>
+      <c r="AP25" s="15">
+        <f t="shared" si="85"/>
+        <v>0.26</v>
+      </c>
+      <c r="AQ25" s="15">
+        <f t="shared" si="85"/>
+        <v>0.26</v>
+      </c>
+      <c r="AR25" s="15">
+        <f t="shared" si="85"/>
+        <v>0.26</v>
+      </c>
+      <c r="AS25" s="15">
+        <f t="shared" si="85"/>
+        <v>0.26</v>
+      </c>
+      <c r="AT25" s="15">
+        <f t="shared" ref="AT25:AX25" si="86">AT15/AT14</f>
+        <v>0.26</v>
+      </c>
+      <c r="AU25" s="15">
         <f t="shared" si="86"/>
         <v>0.26</v>
       </c>
-      <c r="AP25" s="15">
+      <c r="AV25" s="15">
         <f t="shared" si="86"/>
         <v>0.26</v>
       </c>
-      <c r="AQ25" s="15">
+      <c r="AW25" s="15">
         <f t="shared" si="86"/>
         <v>0.26</v>
       </c>
-      <c r="AR25" s="15">
+      <c r="AX25" s="15">
         <f t="shared" si="86"/>
         <v>0.26</v>
       </c>
-      <c r="AS25" s="15">
-        <f t="shared" si="86"/>
-        <v>0.26</v>
-      </c>
-      <c r="AT25" s="15">
-        <f t="shared" ref="AT25:AX25" si="87">AT15/AT14</f>
-        <v>0.26</v>
-      </c>
-      <c r="AU25" s="15">
-        <f t="shared" si="87"/>
-        <v>0.26</v>
-      </c>
-      <c r="AV25" s="15">
-        <f t="shared" si="87"/>
-        <v>0.26</v>
-      </c>
-      <c r="AW25" s="15">
-        <f t="shared" si="87"/>
-        <v>0.26</v>
-      </c>
-      <c r="AX25" s="15">
-        <f t="shared" si="87"/>
-        <v>0.26</v>
-      </c>
       <c r="AZ25" t="s">
         <v>45</v>
       </c>
-      <c r="BA25" s="2">
+      <c r="BA25" s="7">
         <f>NPV(BA24,AO17:EI17)</f>
-        <v>612553.7733710563</v>
+        <v>575890.85544772062</v>
       </c>
     </row>
     <row r="26" spans="2:139" x14ac:dyDescent="0.3">
@@ -4719,135 +4846,143 @@
       </c>
       <c r="C26" s="15">
         <f>C17/C3</f>
-        <v>8.0184834806384914E-2</v>
+        <v>8.01848348063849E-2</v>
       </c>
       <c r="D26" s="15">
-        <f t="shared" ref="D26:J26" si="88">D17/D3</f>
-        <v>6.9452628281980747E-2</v>
+        <f t="shared" ref="D26:J26" si="87">D17/D3</f>
+        <v>6.9452628281980733E-2</v>
       </c>
       <c r="E26" s="15">
-        <f t="shared" si="88"/>
+        <f t="shared" si="87"/>
         <v>7.3505726362875418E-2</v>
       </c>
       <c r="F26" s="15">
-        <f t="shared" si="88"/>
-        <v>4.743961704157456E-2</v>
+        <f t="shared" si="87"/>
+        <v>4.7439617041574567E-2</v>
       </c>
       <c r="G26" s="15">
-        <f t="shared" si="88"/>
+        <f t="shared" si="87"/>
         <v>3.4525329964640902E-2</v>
       </c>
       <c r="H26" s="15">
-        <f t="shared" si="88"/>
+        <f t="shared" si="87"/>
         <v>6.9456058792869133E-2</v>
       </c>
       <c r="I26" s="15">
-        <f t="shared" si="88"/>
+        <f t="shared" si="87"/>
         <v>0.10290695791133091</v>
       </c>
       <c r="J26" s="15">
-        <f t="shared" si="88"/>
-        <v>6.406673585497924E-2</v>
+        <f t="shared" si="87"/>
+        <v>6.4105263452553671E-2</v>
       </c>
       <c r="W26" s="15">
         <f>W17/W3</f>
-        <v>0.11267195753563625</v>
+        <v>0.11267195753563623</v>
+      </c>
+      <c r="X26" s="15">
+        <f>X17/X3</f>
+        <v>5.0095018852170166E-2</v>
       </c>
       <c r="AA26" s="15">
         <f>AA17/AA3</f>
-        <v>6.8662581898171968E-2</v>
+        <v>6.8662581898171982E-2</v>
+      </c>
+      <c r="AB26" s="15">
+        <f>AB17/AB3</f>
+        <v>7.5304827085629342E-2</v>
       </c>
       <c r="AF26" s="15">
-        <f t="shared" ref="AF26:AX26" si="89">AF17/AF3</f>
+        <f t="shared" ref="AF26:AX26" si="88">AF17/AF3</f>
         <v>6.6351277102711131E-2</v>
       </c>
       <c r="AG26" s="15">
-        <f t="shared" si="89"/>
-        <v>8.4888515839780854E-2</v>
+        <f t="shared" si="88"/>
+        <v>8.488851583978084E-2</v>
       </c>
       <c r="AH26" s="15">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>6.2293815646370383E-2</v>
       </c>
       <c r="AI26" s="15">
-        <f t="shared" si="89"/>
-        <v>6.8174636994360285E-2</v>
+        <f t="shared" si="88"/>
+        <v>6.8174636994360271E-2</v>
       </c>
       <c r="AJ26" s="15">
-        <f t="shared" si="89"/>
-        <v>8.2502094280737751E-2</v>
+        <f t="shared" si="88"/>
+        <v>8.2502094280737737E-2</v>
       </c>
       <c r="AK26" s="15">
-        <f t="shared" si="89"/>
-        <v>9.0827080234243324E-2</v>
+        <f t="shared" si="88"/>
+        <v>9.082708023424331E-2</v>
       </c>
       <c r="AL26" s="15">
-        <f t="shared" si="89"/>
-        <v>6.6030530303654231E-2</v>
+        <f t="shared" si="88"/>
+        <v>6.6030530303654245E-2</v>
       </c>
       <c r="AM26" s="15">
-        <f t="shared" si="89"/>
-        <v>0.10965509174177146</v>
+        <f t="shared" si="88"/>
+        <v>0.10965509174177145</v>
       </c>
       <c r="AN26" s="15">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>9.9196730899771976E-2</v>
       </c>
       <c r="AO26" s="15">
-        <f t="shared" si="89"/>
-        <v>9.2305839087288177E-2</v>
+        <f t="shared" si="88"/>
+        <v>7.7505839087288184E-2</v>
       </c>
       <c r="AP26" s="15">
-        <f t="shared" si="89"/>
-        <v>9.3019124314346197E-2</v>
+        <f t="shared" si="88"/>
+        <v>7.8219124314346189E-2</v>
       </c>
       <c r="AQ26" s="15">
-        <f t="shared" si="89"/>
-        <v>9.3261311762338331E-2</v>
+        <f t="shared" si="88"/>
+        <v>8.5861311762338299E-2</v>
       </c>
       <c r="AR26" s="15">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>9.3505897105855135E-2</v>
       </c>
       <c r="AS26" s="15">
-        <f t="shared" si="89"/>
-        <v>9.3752904086436467E-2</v>
+        <f t="shared" si="88"/>
+        <v>9.3752904086436481E-2</v>
       </c>
       <c r="AT26" s="15">
-        <f t="shared" si="89"/>
-        <v>9.400235668068696E-2</v>
+        <f t="shared" si="88"/>
+        <v>9.4002356680686946E-2</v>
       </c>
       <c r="AU26" s="15">
-        <f t="shared" si="89"/>
-        <v>9.4254279102603256E-2</v>
+        <f t="shared" si="88"/>
+        <v>9.4254279102603242E-2</v>
       </c>
       <c r="AV26" s="15">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>9.450869580592465E-2</v>
       </c>
       <c r="AW26" s="15">
-        <f t="shared" si="89"/>
-        <v>9.4765631486506699E-2</v>
+        <f t="shared" si="88"/>
+        <v>9.4765631486506685E-2</v>
       </c>
       <c r="AX26" s="15">
-        <f t="shared" si="89"/>
-        <v>9.5025111084718242E-2</v>
+        <f t="shared" si="88"/>
+        <v>9.5025111084718228E-2</v>
       </c>
       <c r="AZ26" t="s">
         <v>50</v>
       </c>
-      <c r="BA26" s="2">
+      <c r="BA26" s="7">
         <f>Main!D10</f>
-        <v>-165794.88908367607</v>
+        <v>-155149.08574013051</v>
       </c>
     </row>
     <row r="27" spans="2:139" x14ac:dyDescent="0.3">
       <c r="AZ27" t="s">
         <v>46</v>
       </c>
-      <c r="BA27" s="2">
+      <c r="BA27" s="7">
         <f>BA25+BA26</f>
-        <v>446758.88428738026</v>
+        <v>420741.76970759011</v>
       </c>
     </row>
     <row r="28" spans="2:139" x14ac:dyDescent="0.3">
@@ -4855,8 +4990,8 @@
         <v>47</v>
       </c>
       <c r="BA28" s="2">
-        <f>BA27/AS18</f>
-        <v>342.37283164663711</v>
+        <f>BA27/AX18</f>
+        <v>322.82802862548158</v>
       </c>
     </row>
     <row r="29" spans="2:139" x14ac:dyDescent="0.3">
@@ -4865,7 +5000,7 @@
       </c>
       <c r="BA29" s="2">
         <f>Main!D3</f>
-        <v>193.01</v>
+        <v>199.06</v>
       </c>
     </row>
     <row r="30" spans="2:139" x14ac:dyDescent="0.3">
@@ -4874,7 +5009,7 @@
       </c>
       <c r="BA30" s="11">
         <f>BA28/BA29-1</f>
-        <v>0.7738605857035239</v>
+        <v>0.62176242653210889</v>
       </c>
     </row>
     <row r="31" spans="2:139" x14ac:dyDescent="0.3">
@@ -4927,13 +5062,19 @@
       <c r="W32" s="10">
         <v>11837879</v>
       </c>
-      <c r="X32" s="1"/>
+      <c r="X32" s="10">
+        <f>X51-W32</f>
+        <v>11444571</v>
+      </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
       <c r="AA32" s="10">
         <v>12253326</v>
       </c>
-      <c r="AB32" s="1"/>
+      <c r="AB32" s="10">
+        <f>AB51-AA32</f>
+        <v>12377427</v>
+      </c>
       <c r="AC32" s="1"/>
       <c r="AD32" s="1"/>
       <c r="AE32" s="1"/>
@@ -5001,10 +5142,18 @@
         <f>8774492+634492</f>
         <v>9408984</v>
       </c>
+      <c r="X33" s="23">
+        <f>X52-W33</f>
+        <v>9006530</v>
+      </c>
       <c r="AA33" s="5">
         <f>9337703+719810</f>
         <v>10057513</v>
       </c>
+      <c r="AB33" s="23">
+        <f>AB52-AA33</f>
+        <v>10408589</v>
+      </c>
       <c r="AF33" s="20">
         <f>21543035+1191301</f>
         <v>22734336</v>
@@ -5047,31 +5196,31 @@
         <v>31</v>
       </c>
       <c r="C34" s="10">
-        <f t="shared" ref="C34:I34" si="90">C32-C33</f>
+        <f t="shared" ref="C34:I34" si="89">C32-C33</f>
         <v>1452128</v>
       </c>
       <c r="D34" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>1351592</v>
       </c>
       <c r="E34" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>1382175</v>
       </c>
       <c r="F34" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>1195301</v>
       </c>
       <c r="G34" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>549428</v>
       </c>
       <c r="H34" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>1148147</v>
       </c>
       <c r="I34" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>1656702</v>
       </c>
       <c r="J34" s="1"/>
@@ -5091,51 +5240,57 @@
         <f>W32-W33</f>
         <v>2428895</v>
       </c>
-      <c r="X34" s="1"/>
+      <c r="X34" s="10">
+        <f>X32-X33</f>
+        <v>2438041</v>
+      </c>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
       <c r="AA34" s="10">
         <f>AA32-AA33</f>
         <v>2195813</v>
       </c>
-      <c r="AB34" s="1"/>
+      <c r="AB34" s="10">
+        <f>AB32-AB33</f>
+        <v>1968838</v>
+      </c>
       <c r="AC34" s="1"/>
       <c r="AD34" s="1"/>
       <c r="AE34" s="1"/>
       <c r="AF34" s="19">
-        <f t="shared" ref="AF34:AN34" si="91">AF32-AF33</f>
+        <f t="shared" ref="AF34:AN34" si="90">AF32-AF33</f>
         <v>4862857</v>
       </c>
       <c r="AG34" s="19">
-        <f t="shared" si="91"/>
+        <f t="shared" si="90"/>
         <v>5490357</v>
       </c>
       <c r="AH34" s="19">
-        <f t="shared" si="91"/>
+        <f t="shared" si="90"/>
         <v>5443896</v>
       </c>
       <c r="AI34" s="10">
-        <f t="shared" si="91"/>
+        <f t="shared" si="90"/>
         <v>5381196</v>
       </c>
       <c r="AJ34" s="10">
-        <f t="shared" si="91"/>
+        <f t="shared" si="90"/>
         <v>4832374</v>
       </c>
       <c r="AK34" s="10">
-        <f t="shared" si="91"/>
+        <f t="shared" si="90"/>
         <v>5971673</v>
       </c>
       <c r="AL34" s="10">
-        <f t="shared" si="91"/>
+        <f t="shared" si="90"/>
         <v>6313016</v>
       </c>
       <c r="AM34" s="10">
-        <f t="shared" si="91"/>
+        <f t="shared" si="90"/>
         <v>9368318</v>
       </c>
       <c r="AN34" s="10">
-        <f t="shared" si="91"/>
+        <f t="shared" si="90"/>
         <v>9578038</v>
       </c>
       <c r="BB34" t="s">
@@ -5171,8 +5326,16 @@
       <c r="W35" s="5">
         <v>1119984</v>
       </c>
+      <c r="X35" s="23">
+        <f>X54-W35</f>
+        <v>1282735</v>
+      </c>
       <c r="AA35" s="5">
         <v>1029672</v>
+      </c>
+      <c r="AB35" s="23">
+        <f>AB54-AA35</f>
+        <v>1129287</v>
       </c>
       <c r="AF35" s="20">
         <v>2868485</v>
@@ -5207,31 +5370,31 @@
         <v>33</v>
       </c>
       <c r="C36" s="10">
-        <f t="shared" ref="C36:I36" si="92">C34-C35</f>
+        <f t="shared" ref="C36:I36" si="91">C34-C35</f>
         <v>740611</v>
       </c>
       <c r="D36" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="91"/>
         <v>658607</v>
       </c>
       <c r="E36" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="91"/>
         <v>640097</v>
       </c>
       <c r="F36" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="91"/>
         <v>359916</v>
       </c>
       <c r="G36" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="91"/>
         <v>13920</v>
       </c>
       <c r="H36" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="91"/>
         <v>506061</v>
       </c>
       <c r="I36" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="91"/>
         <v>987940</v>
       </c>
       <c r="J36" s="1"/>
@@ -5251,51 +5414,57 @@
         <f>W34-W35</f>
         <v>1308911</v>
       </c>
-      <c r="X36" s="1"/>
+      <c r="X36" s="10">
+        <f>X34-X35</f>
+        <v>1155306</v>
+      </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
       <c r="AA36" s="10">
         <f>AA34-AA35</f>
         <v>1166141</v>
       </c>
-      <c r="AB36" s="1"/>
+      <c r="AB36" s="10">
+        <f>AB34-AB35</f>
+        <v>839551</v>
+      </c>
       <c r="AC36" s="1"/>
       <c r="AD36" s="1"/>
       <c r="AE36" s="1"/>
       <c r="AF36" s="19">
-        <f t="shared" ref="AF36:AN36" si="93">AF34-AF35</f>
+        <f t="shared" ref="AF36:AN36" si="92">AF34-AF35</f>
         <v>1994372</v>
       </c>
       <c r="AG36" s="19">
-        <f t="shared" si="93"/>
+        <f t="shared" si="92"/>
         <v>2399862</v>
       </c>
       <c r="AH36" s="19">
-        <f t="shared" si="93"/>
+        <f t="shared" si="92"/>
         <v>2467545</v>
       </c>
       <c r="AI36" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="92"/>
         <v>2399231</v>
       </c>
       <c r="AJ36" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="92"/>
         <v>2197749</v>
       </c>
       <c r="AK36" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="92"/>
         <v>2995696</v>
       </c>
       <c r="AL36" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="92"/>
         <v>2725026</v>
       </c>
       <c r="AM36" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="92"/>
         <v>5352935</v>
       </c>
       <c r="AN36" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="92"/>
         <v>4795586</v>
       </c>
     </row>
@@ -5341,13 +5510,19 @@
       <c r="W37" s="5">
         <v>-164937</v>
       </c>
-      <c r="X37" s="1"/>
+      <c r="X37" s="23">
+        <f t="shared" ref="X37:X41" si="93">X56-W37</f>
+        <v>-99378</v>
+      </c>
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
       <c r="AA37" s="5">
         <v>-141044</v>
       </c>
-      <c r="AB37" s="1"/>
+      <c r="AB37" s="23">
+        <f t="shared" ref="AB37:AB41" si="94">AB56-AA37</f>
+        <v>-131580</v>
+      </c>
       <c r="AC37" s="1"/>
       <c r="AD37" s="1"/>
       <c r="AE37" s="1"/>
@@ -5416,13 +5591,19 @@
       <c r="W38" s="5">
         <v>-173800</v>
       </c>
-      <c r="X38" s="1"/>
+      <c r="X38" s="23">
+        <f t="shared" si="93"/>
+        <v>-97145</v>
+      </c>
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
       <c r="AA38" s="5">
         <v>-153721</v>
       </c>
-      <c r="AB38" s="1"/>
+      <c r="AB38" s="23">
+        <f t="shared" si="94"/>
+        <v>-139025</v>
+      </c>
       <c r="AC38" s="1"/>
       <c r="AD38" s="1"/>
       <c r="AE38" s="1"/>
@@ -5490,13 +5671,19 @@
       <c r="W39" s="5">
         <v>16509</v>
       </c>
-      <c r="X39" s="1"/>
+      <c r="X39" s="23">
+        <f t="shared" si="93"/>
+        <v>37185</v>
+      </c>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
       <c r="AA39" s="5">
         <v>6211</v>
       </c>
-      <c r="AB39" s="1"/>
+      <c r="AB39" s="23">
+        <f t="shared" si="94"/>
+        <v>18799</v>
+      </c>
       <c r="AC39" s="1"/>
       <c r="AD39" s="1"/>
       <c r="AE39" s="1"/>
@@ -5564,13 +5751,19 @@
       <c r="W40" s="5">
         <v>-236999</v>
       </c>
-      <c r="X40" s="1"/>
+      <c r="X40" s="23">
+        <f t="shared" si="93"/>
+        <v>463810</v>
+      </c>
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
       <c r="AA40" s="5">
         <v>212375</v>
       </c>
-      <c r="AB40" s="1"/>
+      <c r="AB40" s="23">
+        <f t="shared" si="94"/>
+        <v>-159588</v>
+      </c>
       <c r="AC40" s="1"/>
       <c r="AD40" s="1"/>
       <c r="AE40" s="1"/>
@@ -5625,8 +5818,16 @@
       <c r="W41" s="5">
         <v>-4570</v>
       </c>
+      <c r="X41" s="23">
+        <f t="shared" si="93"/>
+        <v>-8527</v>
+      </c>
       <c r="AA41" s="5">
         <v>-9832</v>
+      </c>
+      <c r="AB41" s="23">
+        <f t="shared" si="94"/>
+        <v>24970</v>
       </c>
       <c r="AF41" s="21"/>
       <c r="AG41" s="21"/>
@@ -5655,41 +5856,49 @@
         <v>69</v>
       </c>
       <c r="C42" s="5">
-        <f t="shared" ref="C42:I42" si="94">SUM(C37:C41)</f>
+        <f t="shared" ref="C42:I42" si="95">SUM(C37:C41)</f>
         <v>-110373</v>
       </c>
       <c r="D42" s="5">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>-112228</v>
       </c>
       <c r="E42" s="5">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>-131845</v>
       </c>
       <c r="F42" s="5">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>-39266</v>
       </c>
       <c r="G42" s="5">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>-104314</v>
       </c>
       <c r="H42" s="5">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>-104521</v>
       </c>
       <c r="I42" s="5">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>-153233</v>
       </c>
       <c r="W42" s="5">
         <f>SUM(W37:W41)</f>
         <v>-563797</v>
       </c>
+      <c r="X42" s="5">
+        <f>SUM(X37:X41)</f>
+        <v>295945</v>
+      </c>
       <c r="AA42" s="5">
         <f>SUM(AA37:AA41)</f>
         <v>-86011</v>
       </c>
+      <c r="AB42" s="5">
+        <f>SUM(AB37:AB41)</f>
+        <v>-386424</v>
+      </c>
       <c r="AF42" s="20">
         <v>-199453</v>
       </c>
@@ -5700,27 +5909,27 @@
         <v>182080</v>
       </c>
       <c r="AI42" s="5">
-        <f t="shared" ref="AI42:AN42" si="95">SUM(AI37:AI41)</f>
+        <f t="shared" ref="AI42:AN42" si="96">SUM(AI37:AI41)</f>
         <v>-393712</v>
       </c>
       <c r="AJ42" s="5">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>-734606</v>
       </c>
       <c r="AK42" s="5">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>-994835</v>
       </c>
       <c r="AL42" s="5">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>-945707</v>
       </c>
       <c r="AM42" s="5">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>-1612150</v>
       </c>
       <c r="AN42" s="5">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>-1619003</v>
       </c>
     </row>
@@ -5729,31 +5938,31 @@
         <v>35</v>
       </c>
       <c r="C43" s="10">
-        <f t="shared" ref="C43:I43" si="96">C36-C42</f>
+        <f t="shared" ref="C43:I43" si="97">C36-C42</f>
         <v>850984</v>
       </c>
       <c r="D43" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>770835</v>
       </c>
       <c r="E43" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>771942</v>
       </c>
       <c r="F43" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>399182</v>
       </c>
       <c r="G43" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>118234</v>
       </c>
       <c r="H43" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>610582</v>
       </c>
       <c r="I43" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>1141173</v>
       </c>
       <c r="J43" s="1"/>
@@ -5773,51 +5982,57 @@
         <f>W36-W42</f>
         <v>1872708</v>
       </c>
-      <c r="X43" s="1"/>
+      <c r="X43" s="10">
+        <f>X36-X42</f>
+        <v>859361</v>
+      </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
       <c r="AA43" s="10">
         <f>AA36-AA42</f>
         <v>1252152</v>
       </c>
-      <c r="AB43" s="1"/>
+      <c r="AB43" s="10">
+        <f>AB36-AB42</f>
+        <v>1225975</v>
+      </c>
       <c r="AC43" s="1"/>
       <c r="AD43" s="1"/>
       <c r="AE43" s="1"/>
       <c r="AF43" s="19">
-        <f t="shared" ref="AF43:AN43" si="97">AF36-AF42</f>
+        <f t="shared" ref="AF43:AN43" si="98">AF36-AF42</f>
         <v>2193825</v>
       </c>
       <c r="AG43" s="19">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>2620429</v>
       </c>
       <c r="AH43" s="19">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>2285465</v>
       </c>
       <c r="AI43" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>2792943</v>
       </c>
       <c r="AJ43" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>2932355</v>
       </c>
       <c r="AK43" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>3990531</v>
       </c>
       <c r="AL43" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>3670733</v>
       </c>
       <c r="AM43" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>6965085</v>
       </c>
       <c r="AN43" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>6414589</v>
       </c>
     </row>
@@ -5850,8 +6065,16 @@
       <c r="W44" s="5">
         <v>508435</v>
       </c>
+      <c r="X44" s="23">
+        <f t="shared" ref="X44:X45" si="99">X63-W44</f>
+        <v>357983</v>
+      </c>
       <c r="AA44" s="5">
         <v>379959</v>
+      </c>
+      <c r="AB44" s="23">
+        <f t="shared" ref="AB44:AB45" si="100">AB63-AA44</f>
+        <v>253034</v>
       </c>
       <c r="AF44" s="20">
         <v>628900</v>
@@ -5910,8 +6133,16 @@
       <c r="W45" s="5">
         <v>30476</v>
       </c>
+      <c r="X45" s="23">
+        <f t="shared" si="99"/>
+        <v>-71938</v>
+      </c>
       <c r="AA45" s="5">
         <v>30848</v>
+      </c>
+      <c r="AB45" s="23">
+        <f t="shared" si="100"/>
+        <v>40861</v>
       </c>
       <c r="AF45" s="20">
         <f>-362060+95876</f>
@@ -5949,31 +6180,31 @@
         <v>38</v>
       </c>
       <c r="C46" s="10">
-        <f t="shared" ref="C46:I46" si="98">C43-C44-C45</f>
+        <f t="shared" ref="C46:I46" si="101">C43-C44-C45</f>
         <v>619129</v>
       </c>
       <c r="D46" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="101"/>
         <v>530410</v>
       </c>
       <c r="E46" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="101"/>
         <v>559300</v>
       </c>
       <c r="F46" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="101"/>
         <v>327302</v>
       </c>
       <c r="G46" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="101"/>
         <v>158844</v>
       </c>
       <c r="H46" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="101"/>
         <v>470525</v>
       </c>
       <c r="I46" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="101"/>
         <v>838695</v>
       </c>
       <c r="J46" s="1"/>
@@ -5993,51 +6224,57 @@
         <f>W43-W44-W45</f>
         <v>1333797</v>
       </c>
-      <c r="X46" s="1"/>
+      <c r="X46" s="10">
+        <f>X43-X44-X45</f>
+        <v>573316</v>
+      </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
       <c r="AA46" s="10">
         <f>AA43-AA44-AA45</f>
         <v>841345</v>
       </c>
-      <c r="AB46" s="1"/>
+      <c r="AB46" s="10">
+        <f>AB43-AB44-AB45</f>
+        <v>932080</v>
+      </c>
       <c r="AC46" s="1"/>
       <c r="AD46" s="1"/>
       <c r="AE46" s="1"/>
       <c r="AF46" s="19">
-        <f t="shared" ref="AF46:AN46" si="99">AF43-AF44-AF45</f>
+        <f t="shared" ref="AF46:AN46" si="102">AF43-AF44-AF45</f>
         <v>1831109</v>
       </c>
       <c r="AG46" s="19">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>2493983</v>
       </c>
       <c r="AH46" s="19">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>1882873</v>
       </c>
       <c r="AI46" s="10">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>2036141</v>
       </c>
       <c r="AJ46" s="10">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>2245261</v>
       </c>
       <c r="AK46" s="10">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>2850109</v>
       </c>
       <c r="AL46" s="10">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>2453318</v>
       </c>
       <c r="AM46" s="10">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>4944932</v>
       </c>
       <c r="AN46" s="10">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>4765084</v>
       </c>
     </row>
@@ -6067,10 +6304,20 @@
         <v>3263</v>
       </c>
       <c r="W47" s="5">
-        <v>2831</v>
+        <f>(15795-2762)/10</f>
+        <v>1303.3</v>
+      </c>
+      <c r="X47" s="5">
+        <f>(15795-2762)/10</f>
+        <v>1303.3</v>
       </c>
       <c r="AA47" s="5">
-        <v>2831</v>
+        <f>(15795-2762)/10</f>
+        <v>1303.3</v>
+      </c>
+      <c r="AB47" s="5">
+        <f>(15795-2762)/10</f>
+        <v>1303.3</v>
       </c>
       <c r="AF47" s="20">
         <v>2947</v>
@@ -6105,31 +6352,31 @@
         <v>39</v>
       </c>
       <c r="C48" s="18">
-        <f t="shared" ref="C48:I48" si="100">C46/C47</f>
+        <f t="shared" ref="C48:I48" si="103">C46/C47</f>
         <v>210.08788598574822</v>
       </c>
       <c r="D48" s="18">
-        <f t="shared" si="100"/>
+        <f t="shared" si="103"/>
         <v>179.98303359348489</v>
       </c>
       <c r="E48" s="18">
-        <f t="shared" si="100"/>
+        <f t="shared" si="103"/>
         <v>189.78622327790973</v>
       </c>
       <c r="F48" s="18">
-        <f t="shared" si="100"/>
+        <f t="shared" si="103"/>
         <v>111.06277570410587</v>
       </c>
       <c r="G48" s="18">
-        <f t="shared" si="100"/>
+        <f t="shared" si="103"/>
         <v>53.900237529691211</v>
       </c>
       <c r="H48" s="18">
-        <f t="shared" si="100"/>
+        <f t="shared" si="103"/>
         <v>159.66236851034949</v>
       </c>
       <c r="I48" s="18">
-        <f t="shared" si="100"/>
+        <f t="shared" si="103"/>
         <v>257.03187250996018</v>
       </c>
       <c r="J48" s="18"/>
@@ -6147,60 +6394,269 @@
       <c r="V48" s="18"/>
       <c r="W48" s="18">
         <f>W46/W47</f>
-        <v>471.13987990109501</v>
-      </c>
-      <c r="X48" s="18"/>
+        <v>1023.3998311977289</v>
+      </c>
+      <c r="X48" s="18">
+        <f>X46/X47</f>
+        <v>439.89564950510243</v>
+      </c>
       <c r="Y48" s="18"/>
       <c r="Z48" s="18"/>
       <c r="AA48" s="18">
         <f>AA46/AA47</f>
-        <v>297.19003885552809</v>
-      </c>
-      <c r="AB48" s="18"/>
+        <v>645.54975830583908</v>
+      </c>
+      <c r="AB48" s="18">
+        <f>AB46/AB47</f>
+        <v>715.16918591268325</v>
+      </c>
       <c r="AC48" s="18"/>
       <c r="AD48" s="18"/>
       <c r="AE48" s="18"/>
       <c r="AF48" s="22">
-        <f t="shared" ref="AF48:AN48" si="101">AF46/AF47</f>
+        <f t="shared" ref="AF48:AN48" si="104">AF46/AF47</f>
         <v>621.34679334916859</v>
       </c>
       <c r="AG48" s="22">
-        <f t="shared" si="101"/>
+        <f t="shared" si="104"/>
         <v>846.27858839497799</v>
       </c>
       <c r="AH48" s="22">
-        <f t="shared" si="101"/>
+        <f t="shared" si="104"/>
         <v>655.8247997213515</v>
       </c>
       <c r="AI48" s="18">
-        <f t="shared" si="101"/>
+        <f t="shared" si="104"/>
         <v>719.23030731190397</v>
       </c>
       <c r="AJ48" s="18">
-        <f t="shared" si="101"/>
+        <f t="shared" si="104"/>
         <v>793.09819851642533</v>
       </c>
       <c r="AK48" s="18">
-        <f t="shared" si="101"/>
+        <f t="shared" si="104"/>
         <v>1006.7499116919817</v>
       </c>
       <c r="AL48" s="18">
-        <f t="shared" si="101"/>
+        <f t="shared" si="104"/>
         <v>866.59060402684565</v>
       </c>
       <c r="AM48" s="18">
-        <f t="shared" si="101"/>
+        <f t="shared" si="104"/>
         <v>1746.7085835393855</v>
       </c>
       <c r="AN48" s="18">
-        <f t="shared" si="101"/>
+        <f t="shared" si="104"/>
         <v>1683.1805015895443</v>
+      </c>
+    </row>
+    <row r="51" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="X51" s="10">
+        <v>23282450</v>
+      </c>
+      <c r="AB51" s="10">
+        <v>24630753</v>
+      </c>
+    </row>
+    <row r="52" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B52" t="s">
+        <v>30</v>
+      </c>
+      <c r="X52" s="5">
+        <f>17134152+1281362</f>
+        <v>18415514</v>
+      </c>
+      <c r="AB52" s="5">
+        <f>19001590+1464512</f>
+        <v>20466102</v>
+      </c>
+    </row>
+    <row r="53" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B53" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X53" s="10">
+        <f>X51-X52</f>
+        <v>4866936</v>
+      </c>
+      <c r="AB53" s="10">
+        <f>AB51-AB52</f>
+        <v>4164651</v>
+      </c>
+    </row>
+    <row r="54" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
+        <v>32</v>
+      </c>
+      <c r="X54" s="5">
+        <v>2402719</v>
+      </c>
+      <c r="AB54" s="5">
+        <v>2158959</v>
+      </c>
+    </row>
+    <row r="55" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B55" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="X55" s="10">
+        <f>X53-X54</f>
+        <v>2464217</v>
+      </c>
+      <c r="AB55" s="10">
+        <f>AB53-AB54</f>
+        <v>2005692</v>
+      </c>
+    </row>
+    <row r="56" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B56" t="s">
+        <v>64</v>
+      </c>
+      <c r="X56" s="5">
+        <v>-264315</v>
+      </c>
+      <c r="AB56" s="5">
+        <v>-272624</v>
+      </c>
+    </row>
+    <row r="57" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B57" t="s">
+        <v>65</v>
+      </c>
+      <c r="X57" s="5">
+        <v>-270945</v>
+      </c>
+      <c r="AB57" s="5">
+        <v>-292746</v>
+      </c>
+    </row>
+    <row r="58" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B58" t="s">
+        <v>66</v>
+      </c>
+      <c r="X58" s="5">
+        <v>53694</v>
+      </c>
+      <c r="AB58" s="5">
+        <v>25010</v>
+      </c>
+    </row>
+    <row r="59" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B59" t="s">
+        <v>68</v>
+      </c>
+      <c r="X59" s="5">
+        <v>226811</v>
+      </c>
+      <c r="AB59" s="5">
+        <v>52787</v>
+      </c>
+    </row>
+    <row r="60" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B60" t="s">
+        <v>67</v>
+      </c>
+      <c r="X60" s="5">
+        <v>-13097</v>
+      </c>
+      <c r="AB60" s="5">
+        <v>15138</v>
+      </c>
+    </row>
+    <row r="61" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B61" t="s">
+        <v>69</v>
+      </c>
+      <c r="X61" s="5">
+        <f>SUM(X56:X60)</f>
+        <v>-267852</v>
+      </c>
+      <c r="AB61" s="5">
+        <f>SUM(AB56:AB60)</f>
+        <v>-472435</v>
+      </c>
+    </row>
+    <row r="62" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B62" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="X62" s="10">
+        <f>X55-X61</f>
+        <v>2732069</v>
+      </c>
+      <c r="AB62" s="10">
+        <f>AB55-AB61</f>
+        <v>2478127</v>
+      </c>
+    </row>
+    <row r="63" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B63" t="s">
+        <v>36</v>
+      </c>
+      <c r="X63" s="5">
+        <v>866418</v>
+      </c>
+      <c r="AB63" s="5">
+        <v>632993</v>
+      </c>
+    </row>
+    <row r="64" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B64" t="s">
+        <v>37</v>
+      </c>
+      <c r="X64" s="5">
+        <v>-41462</v>
+      </c>
+      <c r="AB64" s="5">
+        <v>71709</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B65" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="X65" s="10">
+        <f>X62-X63-X64</f>
+        <v>1907113</v>
+      </c>
+      <c r="AB65" s="10">
+        <f>AB62-AB63-AB64</f>
+        <v>1773425</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B66" t="s">
+        <v>1</v>
+      </c>
+      <c r="X66" s="5">
+        <f>(15795-2762)/10</f>
+        <v>1303.3</v>
+      </c>
+      <c r="AB66" s="5">
+        <f>(15795-2762)/10</f>
+        <v>1303.3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B67" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="X67" s="18">
+        <f>X65/X66</f>
+        <v>1463.2954807028314</v>
+      </c>
+      <c r="AB67" s="18">
+        <f>AB65/AB66</f>
+        <v>1360.7189442185222</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967293" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
